--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO12" headerRowCount="1">
-  <autoFilter ref="A1:CO12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
+  <autoFilter ref="A1:CO15"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO12"/>
+  <dimension ref="A1:CO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2206,18 +2206,32 @@
       </c>
       <c r="U4" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="24" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:52:07.189795Z</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-g2-kc-2026-07-26).</t>
@@ -2467,18 +2481,32 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:52:14.005524Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-tl-c9-2026-07-26).</t>
@@ -2650,22 +2678,22 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>8b16335532f542a8</t>
+          <t>0472512025f74cf2</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-27T17:37:52.168845Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:00:00Z</t>
+          <t>2026-07-27T18:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>60818</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2675,12 +2703,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2690,7 +2718,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J6" s="25" t="n"/>
@@ -2700,26 +2728,26 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.509804</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.811601</v>
+        <v>0.596094</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.281085</v>
+        <v>0.08629000000000001</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="S6" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
@@ -2728,21 +2756,35 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:37.962153Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-bfx-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-ap-bld-2026-07-27).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2752,7 +2794,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2783,32 +2825,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2826,7 +2868,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>181f161eadbc9c7936d57f0cb930b26b3363dbf664c19f1b39e954282aa7d3a8</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2841,7 +2883,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>181f161eadbc9c7936d57f0cb930b26b3363dbf664c19f1b39e954282aa7d3a8</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2861,7 +2903,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:55.452705Z</t>
+          <t>2026-07-27T17:37:32.913782Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2871,13 +2913,13 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.509804</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
@@ -2911,22 +2953,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>06832d6818e94538</t>
+          <t>24b53e6e44c343dd</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-27T19:51:04.764967Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T07:30:00Z</t>
+          <t>2026-07-27T21:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>61044</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2936,12 +2978,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -2951,7 +2993,7 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -2961,23 +3003,23 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>122</v>
+        <v>-178</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.22</v>
+        <v>1.561798</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.640288</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.7097250000000001</v>
+        <v>0.654099</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.259275</v>
+        <v>0.013811</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>2</v>
@@ -2989,21 +3031,35 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>1.1236</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:07.555566Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-kt-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3044,32 +3100,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3087,7 +3143,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>a1ec01e655fe8c74e1a10624d033e1ed3a28f75c65521824090c359f6c375c81</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3102,7 +3158,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>a1ec01e655fe8c74e1a10624d033e1ed3a28f75c65521824090c359f6c375c81</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3122,7 +3178,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:56.520012Z</t>
+          <t>2026-07-27T19:50:48.466474Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3132,13 +3188,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>122</v>
+        <v>-178</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.22</v>
+        <v>1.561798</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.640288</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3172,22 +3228,22 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>f49ca7ebd75d4884</t>
+          <t>03a9600655254325</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-28T08:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>61376</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3197,12 +3253,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3231,14 +3287,14 @@
         <v>0.640288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.6818</v>
+        <v>0.65045</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.041512</v>
+        <v>0.010162</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>2</v>
@@ -3264,7 +3320,7 @@
       <c r="AD8" s="24" t="n"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-t1a-nsea-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-hlec-hbc-2026-07-28).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3305,32 +3361,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3348,7 +3404,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3363,7 +3419,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3383,7 +3439,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:57.034856Z</t>
+          <t>2026-07-28T01:59:21.480440Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3433,22 +3489,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>da2d4db8bf6b4600</t>
+          <t>a25638b4aab347f0</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:00:00Z</t>
+          <t>2026-07-28T10:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>61400</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3458,12 +3514,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3473,7 +3529,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J9" s="25" t="n"/>
@@ -3483,20 +3539,20 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.460829</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.912307</v>
+        <v>0.659148</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.431538</v>
+        <v>0.198319</v>
       </c>
       <c r="R9" s="26" t="n">
         <v>100</v>
@@ -3525,7 +3581,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-hle-krx-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-ktc-dkc-2026-07-28).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3566,32 +3622,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3609,7 +3665,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3624,7 +3680,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3644,7 +3700,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:58.156214Z</t>
+          <t>2026-07-28T01:59:21.952203Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3654,13 +3710,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.460829</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3694,22 +3750,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>f63fc550923c4b6c</t>
+          <t>3df3419240ac46ca</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:45:00Z</t>
+          <t>2026-07-28T17:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3719,12 +3775,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3744,26 +3800,26 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-203</v>
+        <v>117</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.17</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.460829</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.865659</v>
+        <v>0.523131</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.195692</v>
+        <v>0.062302</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
@@ -3786,7 +3842,7 @@
       <c r="AD10" s="24" t="n"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-t1-ns-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-znt-dyn-2026-07-28).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3827,32 +3883,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3870,7 +3926,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3885,7 +3941,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3905,7 +3961,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:58.672379Z</t>
+          <t>2026-07-28T01:59:25.235547Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3915,13 +3971,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-203</v>
+        <v>117</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.17</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.460829</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -3955,22 +4011,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>0cf0e32cf52c4a46</t>
+          <t>94310d96695d4b24</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:30:00Z</t>
+          <t>2026-07-28T17:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>61611</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -3980,12 +4036,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4005,26 +4061,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.359712</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.803091</v>
+        <v>0.513552</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.462955</v>
+        <v>0.15384</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4047,7 +4103,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-bro-dk-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-lol-zyb-ess-2026-07-28).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4088,32 +4144,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4131,7 +4187,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4146,7 +4202,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4166,7 +4222,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:59.671342Z</t>
+          <t>2026-07-28T01:59:25.710837Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4176,13 +4232,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.359712</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4216,22 +4272,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>6d2e606bbff7465e</t>
+          <t>b181c7eb7737428d</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-07-28T18:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4241,12 +4297,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4266,26 +4322,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-233</v>
+        <v>-122</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.819672</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.54955</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.712884</v>
+        <v>0.622675</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.013184</v>
+        <v>0.073125</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4308,7 +4364,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-ban-myth-2026-07-28).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4349,32 +4405,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4392,7 +4448,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4407,7 +4463,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4427,7 +4483,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:03.641211Z</t>
+          <t>2026-07-28T01:59:26.636317Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4437,13 +4493,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-233</v>
+        <v>-122</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.819672</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.54955</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4474,6 +4530,789 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>f1881f5cab59436e</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.734702Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>61851</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.547957</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.147957</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-jl-vitb-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:30.117610Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>976b76ac32034330</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.734702Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>62171</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.773255</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.122905</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-pnga-tse-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:32.137972Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>9facb1716d684e29</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.734702Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>62314</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.517575</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.077046</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-7rex-kbm-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.228061Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
-  <autoFilter ref="A1:CO15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO9" headerRowCount="1">
+  <autoFilter ref="A1:CO9"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$9)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO15"/>
+  <dimension ref="A1:CO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3228,12 +3228,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>03a9600655254325</t>
+          <t>488d777722074f1d</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
+          <t>2026-07-28T05:05:19.448075Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3287,11 +3287,11 @@
         <v>0.640288</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.65045</v>
+        <v>0.6502599999999999</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.010162</v>
+        <v>0.009972</v>
       </c>
       <c r="R8" s="26" t="n">
         <v>25</v>
@@ -3306,18 +3306,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:46.133762Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-hlec-hbc-2026-07-28).</t>
@@ -3330,7 +3344,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3404,7 +3418,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>9a599be054d1f2f2548e59017ab201f151d7f9e118fd5b364d64e4e515bcc72a</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3419,7 +3433,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>9a599be054d1f2f2548e59017ab201f151d7f9e118fd5b364d64e4e515bcc72a</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3439,7 +3453,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:21.480440Z</t>
+          <t>2026-07-28T05:04:47.620446Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3489,12 +3503,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>a25638b4aab347f0</t>
+          <t>10e16627bdcf4d3b</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
+          <t>2026-07-28T08:11:25.230149Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3539,20 +3553,20 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.469484</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.659148</v>
+        <v>0.659678</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.198319</v>
+        <v>0.190194</v>
       </c>
       <c r="R9" s="26" t="n">
         <v>100</v>
@@ -3567,21 +3581,35 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:51.185275Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-ktc-dkc-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-ktc-dkc-2026-07-28).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3665,7 +3693,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>f70c60dff382bbc12c8f4c5f7776a2ae9cb7c56547818c66aa81fe255bb5bb7d</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3680,7 +3708,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>f70c60dff382bbc12c8f4c5f7776a2ae9cb7c56547818c66aa81fe255bb5bb7d</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3700,7 +3728,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:21.952203Z</t>
+          <t>2026-07-28T08:10:53.411585Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3710,13 +3738,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.469484</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3747,1572 +3775,6 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>3df3419240ac46ca</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>61612</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.523131</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>0.062302</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>51</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-znt-dyn-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:25.235547Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN10" s="28" t="n"/>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
-      <c r="CB10" s="24" t="n"/>
-      <c r="CC10" s="24" t="n"/>
-      <c r="CD10" s="24" t="n"/>
-      <c r="CE10" s="24" t="n"/>
-      <c r="CF10" s="24" t="n"/>
-      <c r="CG10" s="24" t="n"/>
-      <c r="CH10" s="24" t="n"/>
-      <c r="CI10" s="24" t="n"/>
-      <c r="CJ10" s="24" t="n"/>
-      <c r="CK10" s="24" t="n"/>
-      <c r="CL10" s="24" t="n"/>
-      <c r="CM10" s="24" t="n"/>
-      <c r="CN10" s="24" t="n"/>
-      <c r="CO10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>94310d96695d4b24</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>61611</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.513552</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.15384</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>97</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-lol-zyb-ess-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:25.710837Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="BN11" s="28" t="n"/>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-      <c r="CB11" s="24" t="n"/>
-      <c r="CC11" s="24" t="n"/>
-      <c r="CD11" s="24" t="n"/>
-      <c r="CE11" s="24" t="n"/>
-      <c r="CF11" s="24" t="n"/>
-      <c r="CG11" s="24" t="n"/>
-      <c r="CH11" s="24" t="n"/>
-      <c r="CI11" s="24" t="n"/>
-      <c r="CJ11" s="24" t="n"/>
-      <c r="CK11" s="24" t="n"/>
-      <c r="CL11" s="24" t="n"/>
-      <c r="CM11" s="24" t="n"/>
-      <c r="CN11" s="24" t="n"/>
-      <c r="CO11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>b181c7eb7737428d</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>61724</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0.622675</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>0.073125</v>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T12" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-ban-myth-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH12" s="24" t="n"/>
-      <c r="AI12" s="31" t="n"/>
-      <c r="AJ12" s="31" t="n"/>
-      <c r="AK12" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL12" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM12" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN12" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO12" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP12" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AQ12" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AR12" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AS12" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="AT12" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="AU12" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="AV12" s="24" t="n"/>
-      <c r="AW12" s="24" t="n"/>
-      <c r="AX12" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY12" s="24" t="n"/>
-      <c r="AZ12" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA12" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB12" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC12" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:26.636317Z</t>
-        </is>
-      </c>
-      <c r="BI12" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ12" s="25" t="n"/>
-      <c r="BK12" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL12" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM12" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN12" s="28" t="n"/>
-      <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
-      <c r="BS12" s="28" t="n"/>
-      <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
-      <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
-      <c r="BZ12" s="24" t="n"/>
-      <c r="CA12" s="31" t="n"/>
-      <c r="CB12" s="24" t="n"/>
-      <c r="CC12" s="24" t="n"/>
-      <c r="CD12" s="24" t="n"/>
-      <c r="CE12" s="24" t="n"/>
-      <c r="CF12" s="24" t="n"/>
-      <c r="CG12" s="24" t="n"/>
-      <c r="CH12" s="24" t="n"/>
-      <c r="CI12" s="24" t="n"/>
-      <c r="CJ12" s="24" t="n"/>
-      <c r="CK12" s="24" t="n"/>
-      <c r="CL12" s="24" t="n"/>
-      <c r="CM12" s="24" t="n"/>
-      <c r="CN12" s="24" t="n"/>
-      <c r="CO12" s="24" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>f1881f5cab59436e</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>61851</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0.547957</v>
-      </c>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n">
-        <v>0.147957</v>
-      </c>
-      <c r="R13" s="26" t="n">
-        <v>94</v>
-      </c>
-      <c r="S13" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-jl-vitb-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG13" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH13" s="24" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN13" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP13" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AQ13" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AR13" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AS13" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AT13" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AU13" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AV13" s="24" t="n"/>
-      <c r="AW13" s="24" t="n"/>
-      <c r="AX13" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY13" s="24" t="n"/>
-      <c r="AZ13" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA13" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB13" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC13" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:30.117610Z</t>
-        </is>
-      </c>
-      <c r="BI13" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ13" s="25" t="n"/>
-      <c r="BK13" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="BL13" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM13" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN13" s="28" t="n"/>
-      <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
-      <c r="BS13" s="28" t="n"/>
-      <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
-      <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
-      <c r="BZ13" s="24" t="n"/>
-      <c r="CA13" s="31" t="n"/>
-      <c r="CB13" s="24" t="n"/>
-      <c r="CC13" s="24" t="n"/>
-      <c r="CD13" s="24" t="n"/>
-      <c r="CE13" s="24" t="n"/>
-      <c r="CF13" s="24" t="n"/>
-      <c r="CG13" s="24" t="n"/>
-      <c r="CH13" s="24" t="n"/>
-      <c r="CI13" s="24" t="n"/>
-      <c r="CJ13" s="24" t="n"/>
-      <c r="CK13" s="24" t="n"/>
-      <c r="CL13" s="24" t="n"/>
-      <c r="CM13" s="24" t="n"/>
-      <c r="CN13" s="24" t="n"/>
-      <c r="CO13" s="24" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>976b76ac32034330</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>62171</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L14" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M14" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N14" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O14" s="28" t="n">
-        <v>0.773255</v>
-      </c>
-      <c r="P14" s="28" t="n"/>
-      <c r="Q14" s="28" t="n">
-        <v>0.122905</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <v>81</v>
-      </c>
-      <c r="S14" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
-      <c r="AE14" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-pnga-tse-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF14" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG14" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH14" s="24" t="n"/>
-      <c r="AI14" s="31" t="n"/>
-      <c r="AJ14" s="31" t="n"/>
-      <c r="AK14" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN14" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO14" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP14" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AQ14" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AR14" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AS14" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AT14" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AU14" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AV14" s="24" t="n"/>
-      <c r="AW14" s="24" t="n"/>
-      <c r="AX14" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY14" s="24" t="n"/>
-      <c r="AZ14" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA14" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB14" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC14" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD14" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG14" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH14" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:32.137972Z</t>
-        </is>
-      </c>
-      <c r="BI14" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ14" s="25" t="n"/>
-      <c r="BK14" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL14" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM14" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN14" s="28" t="n"/>
-      <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
-      <c r="BS14" s="28" t="n"/>
-      <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
-      <c r="BV14" s="29" t="n"/>
-      <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n"/>
-      <c r="BY14" s="27" t="n"/>
-      <c r="BZ14" s="24" t="n"/>
-      <c r="CA14" s="31" t="n"/>
-      <c r="CB14" s="24" t="n"/>
-      <c r="CC14" s="24" t="n"/>
-      <c r="CD14" s="24" t="n"/>
-      <c r="CE14" s="24" t="n"/>
-      <c r="CF14" s="24" t="n"/>
-      <c r="CG14" s="24" t="n"/>
-      <c r="CH14" s="24" t="n"/>
-      <c r="CI14" s="24" t="n"/>
-      <c r="CJ14" s="24" t="n"/>
-      <c r="CK14" s="24" t="n"/>
-      <c r="CL14" s="24" t="n"/>
-      <c r="CM14" s="24" t="n"/>
-      <c r="CN14" s="24" t="n"/>
-      <c r="CO14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>9facb1716d684e29</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>62314</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.517575</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.077046</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>59</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-7rex-kbm-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.228061Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO9" headerRowCount="1">
-  <autoFilter ref="A1:CO9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO37" headerRowCount="1">
+  <autoFilter ref="A1:CO37"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$9)</f>
+        <f>COUNTA('Picks'!$A$2:$A$37)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$9)</f>
+        <f>SUM('Picks'!$BY$2:$BY$37)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO9"/>
+  <dimension ref="A1:CO37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3775,6 +3775,7594 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
     </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>d4ace68e8c6f4e36</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T16:35:07.279987Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>61611</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.513798</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.173662</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:33.364616Z</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-zyb-ess-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>74a5af5bf46639ae7286081d768cab75a1c1ed3b6a99ec6b80a7cea74053e951</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>74a5af5bf46639ae7286081d768cab75a1c1ed3b6a99ec6b80a7cea74053e951</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T16:34:40.783646Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>e71716f563e14979</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:53.885043Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>61810</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.665039</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.005175</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:34.473196Z</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-one-piv-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:21.403877Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>620ed68dd27041a8</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:53.885043Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>63045</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>GD Esports</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.618086</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.177557</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>2.2225</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:35.558657Z</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nort-gde-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>GD Esports</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>GD Esports</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>GD Esports</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:22.452664Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>95b8a51af6134fba</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:53.885043Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>61851</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.547972</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.147972</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:36.786403Z</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-jl-vitb-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:22.971954Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>52aa5653437940f5</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:53.885043Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>62171</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.774271</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.083869</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:37:13.927152Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-pnga-tse-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>6d0c3a7af78df69e418afd83ce19024c6ff8c9299585780de553338ecc64dbde</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:29:23.487478Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>60e6836e6d8840d0</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:36:09.952142Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>62314</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.51757</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.177434</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:37:15.268348Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-7rex-kbm-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>ca96831d4d0156d686c75e5e8f59ac6f6feb9c94633c5ba148d00eae5d31c0c3</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>ca96831d4d0156d686c75e5e8f59ac6f6feb9c94633c5ba148d00eae5d31c0c3</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:35:49.039716Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>00d9443e356c444d</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:44:13.908658Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>62490</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Esports Academy</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.543978</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.134142</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:51:53.561895Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-nsea-dnsc-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Esports Academy</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Esports Academy</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Esports Academy</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>95f3613dbfb3114393b75af6d3fac88d9067109e47362829064271715e48ec1c</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>95f3613dbfb3114393b75af6d3fac88d9067109e47362829064271715e48ec1c</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:43:54.644174Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>1b5b478c211044fa</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:09:15.415515Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>62733</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Absolved</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>B2U</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.523531</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.113695</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:49:07.097307Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-b2u-abs-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Absolved</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Absolved</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Absolved</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>B2U</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>B2U</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>B2U</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:08:42.947251Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>2f325a2de1c04a5d</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:09:15.415515Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>62730</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.721241</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.131077</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:34:54.080506Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-tlnp-zyb-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:08:43.458610Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2c57be300d944a1d</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:09:15.415515Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>62732</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>LEO</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.608007</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.227779</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:08.944368Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-leo-rgi-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>LEO</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>LEO</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>LEO</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:08:44.013442Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>ab246910d33c4261</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:09:15.415515Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>65111</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>SK Gaming Avarosa</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>G2 HEL</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.543596</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.193946</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:10.171086Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-lol-g2h-ska-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>SK Gaming Avarosa</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>SK Gaming Avarosa</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>SK Gaming Avarosa</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>G2 HEL</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>G2 HEL</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>G2 HEL</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:08:45.706081Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>3076aa7596c3480a</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:09:15.415515Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>62812</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.69857</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.008168</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:11.249374Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tog-use-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:08:46.262782Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>5cdbdf87aa92469c</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:09:15.415515Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>62811</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.57328</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.002465</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:12.422244Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-ijc-vitb-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>be1d38db8d7bacf5b86ce795a0ed5e44d5c9f7175af7e8ac6c799cd004175803</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:08:46.735745Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>ec213993b10545c2</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:47:53.341995Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>62999</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.537829</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.157601</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:13.440852Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-ds-bam-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Disruptors</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>b5db55d44821936562fc7ca695a552e8c5a976b7d669055e90322ae075215cf1</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>b5db55d44821936562fc7ca695a552e8c5a976b7d669055e90322ae075215cf1</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:47:30.538258Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>35a013626b2d442b</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:47:53.341995Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>63028</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.6798070000000001</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.170003</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>1.9231</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:15.018338Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kcb-jl-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>b5db55d44821936562fc7ca695a552e8c5a976b7d669055e90322ae075215cf1</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>b5db55d44821936562fc7ca695a552e8c5a976b7d669055e90322ae075215cf1</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:47:31.550767Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>67e4e0522b0946fa</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:47:53.341995Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>63452</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Contingent Esports</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.737425</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.177954</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>1.5748</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:16.135373Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-blue-cont-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Contingent Esports</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Contingent Esports</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Contingent Esports</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>b5db55d44821936562fc7ca695a552e8c5a976b7d669055e90322ae075215cf1</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>b5db55d44821936562fc7ca695a552e8c5a976b7d669055e90322ae075215cf1</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:47:36.207024Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>a29e29260daf4e3b</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:26:04.170318Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>63576</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.620602</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.280466</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>3.395</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:25:11.927569Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-dkc-t1a-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>dd258a11c5e1b4a7b9b28a6360625dd1d4d1b51714a72019d1b2152e3864f6eb</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>dd258a11c5e1b4a7b9b28a6360625dd1d4d1b51714a72019d1b2152e3864f6eb</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:25:34.617720Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>62d5dea298a242e3</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T05:45:28.536407Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>63594</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Ninjas in Pyjamas</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.557132</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.157132</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:25:13.146094Z</t>
+        </is>
+      </c>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-nip-wb-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Ninjas in Pyjamas</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Ninjas in Pyjamas</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Ninjas in Pyjamas</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>4e04b49a5e708505d40da3e5240519971478fdddb80c40794b621c5f354963b6</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>4e04b49a5e708505d40da3e5240519971478fdddb80c40794b621c5f354963b6</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T05:45:06.490478Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>809b9b83d7904fa5</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:23:43.318923Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>63636</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.745706</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.055304</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:31:04.023358Z</t>
+        </is>
+      </c>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-edg-we-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>fc2ebfbbf3351a7d46eae71e144de048639f781bbcee83d0ea7ab1b24a6f8efd</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>fc2ebfbbf3351a7d46eae71e144de048639f781bbcee83d0ea7ab1b24a6f8efd</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:23:22.365823Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>5c389b2c65784390</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:23:43.318923Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>63665</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.788986</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.108475</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:31:05.339288Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-hle-dk-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>fc2ebfbbf3351a7d46eae71e144de048639f781bbcee83d0ea7ab1b24a6f8efd</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>fc2ebfbbf3351a7d46eae71e144de048639f781bbcee83d0ea7ab1b24a6f8efd</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:23:22.907284Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>361e2c1264104cf3</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:35:19.313009Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>63849</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.759185</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.09932100000000001</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-kcb-ijc-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>f9717f767414f329842e741e7cbf2e7aa4999416b847989d6f05bb0e123a02fe</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>f9717f767414f329842e741e7cbf2e7aa4999416b847989d6f05bb0e123a02fe</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:35:02.282138Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>dcc09a2473ed4fac</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>64797</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>SU Esports</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.652006</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.12149</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-su-bw-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>SU Esports</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>SU Esports</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>SU Esports</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:02.795116Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>e6f5a64db7674486</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>64019</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Senshi Esports</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.740872</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.181401</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Senshi Esports</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Senshi Esports</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Senshi Esports</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:03.290679Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>c6ed88701a2d4023</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>64075</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>JSK Esports</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>GnG Amazigh</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.651531</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.101981</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-gng-jsk-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>JSK Esports</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>JSK Esports</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>JSK Esports</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>GnG Amazigh</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>GnG Amazigh</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>GnG Amazigh</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:04.718508Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>c698fcbcc1924bce</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>64670</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.5802349999999999</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.000403</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-ktc-dnsc-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:07.669000Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>21efa623e1364366</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:30:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>64844</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>CTBC Flying Oyster</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.649952</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.040577</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-cfo-gam-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>CTBC Flying Oyster</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>CTBC Flying Oyster</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>CTBC Flying Oyster</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:11.471234Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>4067efadddac43af</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>65014</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.582579</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.162411</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-eko-gmb-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:12.493134Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>7623a59783fa4925</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.542075Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>65517</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.616673</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.016673</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-mvu-cpd-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:55:15.040998Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -9356,18 +9356,32 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:23:04.983674Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-kcb-ijc-2026-07-30).</t>
@@ -9380,7 +9394,7 @@
       </c>
       <c r="AG30" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH30" s="24" t="n"/>
@@ -9539,12 +9553,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>dcc09a2473ed4fac</t>
+          <t>0472540c9b95447e</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9589,23 +9603,23 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-113</v>
+        <v>-163</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.613497</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.619772</v>
       </c>
       <c r="O31" s="28" t="n">
         <v>0.652006</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.12149</v>
+        <v>0.032234</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="S31" s="29" t="n">
         <v>2</v>
@@ -9631,7 +9645,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-su-bw-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-su-bw-2026-07-30).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9715,7 +9729,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9730,7 +9744,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9750,7 +9764,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:02.795116Z</t>
+          <t>2026-07-30T17:21:16.453569Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9760,13 +9774,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-113</v>
+        <v>-163</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.613497</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.619772</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -9800,12 +9814,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>e6f5a64db7674486</t>
+          <t>dec0c57beb794117</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -9850,20 +9864,20 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O32" s="28" t="n">
         <v>0.740872</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.181401</v>
+        <v>0.170057</v>
       </c>
       <c r="R32" s="26" t="n">
         <v>100</v>
@@ -9892,7 +9906,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -9976,7 +9990,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -9991,7 +10005,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10011,7 +10025,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:03.290679Z</t>
+          <t>2026-07-30T17:21:17.395840Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10021,13 +10035,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10061,12 +10075,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>c6ed88701a2d4023</t>
+          <t>7d232df22b8c4d43</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10237,7 +10251,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10252,7 +10266,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10272,7 +10286,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:04.718508Z</t>
+          <t>2026-07-30T17:21:18.840084Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10322,12 +10336,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>c698fcbcc1924bce</t>
+          <t>7e7293f2d14d4167</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10498,7 +10512,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10513,7 +10527,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10533,7 +10547,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:07.669000Z</t>
+          <t>2026-07-30T17:21:21.662513Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10583,12 +10597,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>21efa623e1364366</t>
+          <t>18a37ad2eea547a2</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -10759,7 +10773,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -10774,7 +10788,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10794,7 +10808,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:11.471234Z</t>
+          <t>2026-07-30T17:21:25.109653Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10844,12 +10858,12 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>4067efadddac43af</t>
+          <t>7a93ca5c50f94dcd</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -10894,20 +10908,20 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="O36" s="28" t="n">
         <v>0.582579</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.162411</v>
+        <v>0.172743</v>
       </c>
       <c r="R36" s="26" t="n">
         <v>100</v>
@@ -10936,7 +10950,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-eko-gmb-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-eko-gmb-2026-07-31).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11020,7 +11034,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11035,7 +11049,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11055,7 +11069,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:12.493134Z</t>
+          <t>2026-07-30T17:21:26.089989Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11065,13 +11079,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11105,12 +11119,12 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>7623a59783fa4925</t>
+          <t>a7fc679fa7f84dee</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11281,7 +11295,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11296,7 +11310,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11316,7 +11330,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.040998Z</t>
+          <t>2026-07-30T17:21:28.657597Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -9814,12 +9814,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>dec0c57beb794117</t>
+          <t>7d5b77cb0d4d4147</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -9864,23 +9864,23 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.694444</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.590164</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.740872</v>
+        <v>0.7404230000000001</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.170057</v>
+        <v>0.150259</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S32" s="29" t="n">
         <v>2</v>
@@ -9906,7 +9906,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:17.395840Z</t>
+          <t>2026-07-30T17:38:54.184184Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10035,13 +10035,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.694444</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.590164</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10075,12 +10075,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>7d232df22b8c4d43</t>
+          <t>5e3db2bce41f4369</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10125,23 +10125,23 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.75188</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.570815</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.651531</v>
+        <v>0.650967</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.101981</v>
+        <v>0.080152</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S33" s="29" t="n">
         <v>2</v>
@@ -10167,7 +10167,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-gng-jsk-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gng-jsk-2026-07-30).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:18.840084Z</t>
+          <t>2026-07-30T17:38:55.192074Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10296,13 +10296,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.75188</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.570815</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10336,12 +10336,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>7e7293f2d14d4167</t>
+          <t>428c5306c16242b4</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10395,11 +10395,11 @@
         <v>0.579832</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.5802349999999999</v>
+        <v>0.580174</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.000403</v>
+        <v>0.000342</v>
       </c>
       <c r="R34" s="26" t="n">
         <v>20</v>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:21.662513Z</t>
+          <t>2026-07-30T17:38:58.928794Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10597,12 +10597,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>18a37ad2eea547a2</t>
+          <t>a62c13a0f2224fd7</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -10656,11 +10656,11 @@
         <v>0.609375</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.649952</v>
+        <v>0.649392</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.040577</v>
+        <v>0.040017</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>40</v>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:25.109653Z</t>
+          <t>2026-07-30T17:39:02.536741Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10858,12 +10858,12 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>7a93ca5c50f94dcd</t>
+          <t>0fb0b13f9b434f63</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -10917,11 +10917,11 @@
         <v>0.409836</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.582579</v>
+        <v>0.58218</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.172743</v>
+        <v>0.172344</v>
       </c>
       <c r="R36" s="26" t="n">
         <v>100</v>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:26.089989Z</t>
+          <t>2026-07-30T17:39:03.601758Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11119,12 +11119,12 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>a7fc679fa7f84dee</t>
+          <t>5d2710ba8b5d4ee7</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11178,11 +11178,11 @@
         <v>0.6</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.616673</v>
+        <v>0.616189</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.016673</v>
+        <v>0.016189</v>
       </c>
       <c r="R37" s="26" t="n">
         <v>28</v>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:28.657597Z</t>
+          <t>2026-07-30T17:39:06.401584Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
-  <autoFilter ref="A1:CO8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO10" headerRowCount="1">
+  <autoFilter ref="A1:CO10"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$8)</f>
+        <f>COUNTA('Picks'!$A$2:$A$10)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$8)</f>
+        <f>SUM('Picks'!$BY$2:$BY$10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO8"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2433,22 +2433,22 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>46af7b85baba4c8a</t>
+          <t>9160b273247447bc</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-02T10:00:00Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>66811</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2483,26 +2483,26 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>-117</v>
+        <v>170</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.7</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.37037</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.581905</v>
+        <v>0.615811</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.042734</v>
+        <v>0.245441</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S5" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       <c r="AD5" s="24" t="n"/>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2566,32 +2566,32 @@
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:24.237849Z</t>
+          <t>2026-08-02T07:15:42.166882Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>-117</v>
+        <v>170</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.7</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.37037</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
@@ -2694,22 +2694,22 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>9e794033f37e431f</t>
+          <t>1b09ca0ab75446ec</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-02T11:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>66837</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J6" s="25" t="n"/>
@@ -2744,26 +2744,26 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-223</v>
+        <v>108</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.08</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.480769</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.705384</v>
+        <v>0.58589</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.014982</v>
+        <v>0.105121</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="S6" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       <c r="AD6" s="24" t="n"/>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-els-lil-2026-08-02).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2827,32 +2827,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:25.226163Z</t>
+          <t>2026-08-02T07:15:42.626245Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2915,13 +2915,13 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-223</v>
+        <v>108</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.08</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.480769</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
@@ -2955,22 +2955,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>1e0703e3a5b049d5</t>
+          <t>eebad10014fd42d2</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3005,26 +3005,26 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.75188</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.570815</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.748331</v>
+        <v>0.5826210000000001</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.118701</v>
+        <v>0.011806</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3088,32 +3088,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:25.741380Z</t>
+          <t>2026-08-02T07:15:48.091630Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3176,13 +3176,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.75188</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.570815</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3216,22 +3216,22 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>9a121ede1ef54826</t>
+          <t>aebf5804a3614546</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J8" s="25" t="n"/>
@@ -3266,26 +3266,26 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-144</v>
+        <v>-223</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.44843</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.690402</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.651311</v>
+        <v>0.70607</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.061147</v>
+        <v>0.015668</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       <c r="AD8" s="24" t="n"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3349,32 +3349,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:29.680102Z</t>
+          <t>2026-08-02T07:15:49.062474Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3437,13 +3437,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-144</v>
+        <v>-223</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.44843</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.690402</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3474,6 +3474,528 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>6f2e0ec59be84d9c</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:56.246313Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.748974</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.098624</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:49.527302Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>58ae9b7128414e8a</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:56.246313Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.650712</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.060548</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:53.573864Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -2433,12 +2433,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>9160b273247447bc</t>
+          <t>59114010e0da4ecf</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:42.166882Z</t>
+          <t>2026-08-02T08:18:46.585713Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2694,12 +2694,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>1b09ca0ab75446ec</t>
+          <t>fc8276179ec24625</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2744,23 +2744,23 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.5</v>
       </c>
       <c r="O6" s="28" t="n">
         <v>0.58589</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.105121</v>
+        <v>0.08588999999999999</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>1.25</v>
@@ -2786,7 +2786,7 @@
       <c r="AD6" s="24" t="n"/>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-els-lil-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-els-lil-2026-08-02).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:42.626245Z</t>
+          <t>2026-08-02T08:18:47.154301Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2915,13 +2915,13 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
@@ -2955,12 +2955,12 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>eebad10014fd42d2</t>
+          <t>6cae0f3410b24187</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:48.091630Z</t>
+          <t>2026-08-02T08:18:52.523888Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3216,12 +3216,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>aebf5804a3614546</t>
+          <t>eded518ccb1e471e</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:49.062474Z</t>
+          <t>2026-08-02T08:18:53.565307Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3477,12 +3477,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>6f2e0ec59be84d9c</t>
+          <t>6cb4f17600a14de3</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:49.527302Z</t>
+          <t>2026-08-02T08:18:54.139986Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3738,12 +3738,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>58ae9b7128414e8a</t>
+          <t>d5b6c443503144b8</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:53.573864Z</t>
+          <t>2026-08-02T08:18:58.476467Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -2433,12 +2433,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>59114010e0da4ecf</t>
+          <t>5c6e531064f34f1f</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
@@ -2483,23 +2483,23 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.469484</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.615811</v>
+        <v>0.614494</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.245441</v>
+        <v>0.14501</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>1.5</v>
@@ -2525,7 +2525,7 @@
       <c r="AD5" s="24" t="n"/>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:46.585713Z</t>
+          <t>2026-08-02T09:59:22.583724Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.469484</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
@@ -2694,12 +2694,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>fc8276179ec24625</t>
+          <t>cb4570603d6b43e3</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2753,11 +2753,11 @@
         <v>0.5</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.58589</v>
+        <v>0.586093</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.08588999999999999</v>
+        <v>0.086093</v>
       </c>
       <c r="R6" s="26" t="n">
         <v>63</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:47.154301Z</t>
+          <t>2026-08-02T09:59:23.587864Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>6cae0f3410b24187</t>
+          <t>b3ad37927eb44c52</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -3014,14 +3014,14 @@
         <v>0.570815</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.5826210000000001</v>
+        <v>0.581317</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.011806</v>
+        <v>0.010502</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1.25</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:52.523888Z</t>
+          <t>2026-08-02T09:59:28.910019Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3216,12 +3216,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>eded518ccb1e471e</t>
+          <t>f6739cc34a424594</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3275,14 +3275,14 @@
         <v>0.690402</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.70607</v>
+        <v>0.704215</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.015668</v>
+        <v>0.013813</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>2</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:53.565307Z</t>
+          <t>2026-08-02T09:59:29.886639Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3477,12 +3477,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>6cb4f17600a14de3</t>
+          <t>859d7de8993449dd</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3527,23 +3527,23 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.748974</v>
+        <v>0.7472800000000001</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.098624</v>
+        <v>0.11765</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
@@ -3569,7 +3569,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:54.139986Z</t>
+          <t>2026-08-02T09:59:30.347963Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3698,13 +3698,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3738,12 +3738,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>d5b6c443503144b8</t>
+          <t>b207830b25fd40a9</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3797,11 +3797,11 @@
         <v>0.590164</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.650712</v>
+        <v>0.650541</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.060548</v>
+        <v>0.060377</v>
       </c>
       <c r="R10" s="26" t="n">
         <v>50</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:58.476467Z</t>
+          <t>2026-08-02T09:59:34.514458Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO10" headerRowCount="1">
-  <autoFilter ref="A1:CO10"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP12" headerRowCount="1">
+  <autoFilter ref="A1:CP12"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -752,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$12)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$12)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2511,18 +2521,38 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="Z5" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0.000516</v>
+      </c>
+      <c r="AC5" s="30" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:33.659531Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
@@ -2665,8 +2695,12 @@
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
       <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
-      <c r="BR5" s="28" t="n"/>
+      <c r="BQ5" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BR5" s="28" t="n">
+        <v>0.47</v>
+      </c>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
       <c r="BU5" s="25" t="n"/>
@@ -2690,6 +2724,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2772,18 +2807,38 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="Z6" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:34.762056Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-els-lil-2026-08-02).</t>
@@ -2796,7 +2851,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2926,8 +2981,12 @@
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
+      <c r="BQ6" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR6" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
       <c r="BU6" s="25" t="n"/>
@@ -2951,26 +3010,27 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>b3ad37927eb44c52</t>
+          <t>8e559255db5a4b49</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-02T16:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>66902</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2980,12 +3040,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3005,26 +3065,26 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.819672</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.54955</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.581317</v>
+        <v>0.5584440000000001</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.010502</v>
+        <v>0.008894000000000001</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
@@ -3047,7 +3107,7 @@
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3088,32 +3148,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3131,7 +3191,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3146,7 +3206,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3166,7 +3226,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:28.910019Z</t>
+          <t>2026-08-02T13:07:19.930355Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3176,13 +3236,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.819672</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.54955</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3212,26 +3272,27 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>f6739cc34a424594</t>
+          <t>d9a97e5dcb334bb3</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3241,12 +3302,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3266,26 +3327,26 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-223</v>
+        <v>-133</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.75188</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.570815</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.704215</v>
+        <v>0.58052</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.013813</v>
+        <v>0.009705</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
@@ -3308,7 +3369,7 @@
       <c r="AD8" s="24" t="n"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3349,32 +3410,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3392,7 +3453,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3407,7 +3468,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3427,7 +3488,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:29.886639Z</t>
+          <t>2026-08-02T13:07:22.606056Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3437,13 +3498,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-223</v>
+        <v>-133</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.75188</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.570815</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3473,26 +3534,27 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>859d7de8993449dd</t>
+          <t>e502908325784a88</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3502,12 +3564,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3527,23 +3589,23 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-170</v>
+        <v>-223</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.44843</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.690402</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.7472800000000001</v>
+        <v>0.703234</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.11765</v>
+        <v>0.012832</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
@@ -3569,7 +3631,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3610,32 +3672,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3653,7 +3715,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3668,7 +3730,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3688,7 +3750,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:30.347963Z</t>
+          <t>2026-08-02T13:07:23.605808Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3698,13 +3760,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-170</v>
+        <v>-223</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.44843</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.690402</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3734,26 +3796,27 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>b207830b25fd40a9</t>
+          <t>2168ff7cf0e74ae2</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3763,12 +3826,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3778,7 +3841,7 @@
       </c>
       <c r="I10" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J10" s="25" t="n"/>
@@ -3788,26 +3851,26 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-144</v>
+        <v>-170</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.588235</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.62963</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.650541</v>
+        <v>0.746484</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.060377</v>
+        <v>0.116854</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
@@ -3830,7 +3893,7 @@
       <c r="AD10" s="24" t="n"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3871,32 +3934,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3914,7 +3977,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3929,7 +3992,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3949,7 +4012,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:34.514458Z</t>
+          <t>2026-08-02T13:07:24.188851Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3959,13 +4022,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-144</v>
+        <v>-170</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.588235</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.62963</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -3995,6 +4058,531 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>2ba7a93152ac4650</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:30.652675Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.74769</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.04799</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:24.702936Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>5cd6021b574a43bf</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:30.652675Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.650601</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.060437</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:28.257607Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP12" headerRowCount="1">
-  <autoFilter ref="A1:CP12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP11" headerRowCount="1">
+  <autoFilter ref="A1:CP11"/>
   <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -753,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$11)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$11,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$11,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")/(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$11)/SUM('Picks'!$BX$2:$BX$11),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$11)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$11,"&lt;&gt;",'Picks'!$AB$2:$AB$11),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$11,'Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP12"/>
+  <dimension ref="A1:CP11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3015,12 +3015,12 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>8e559255db5a4b49</t>
+          <t>96a22c8745e44e42</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -3065,23 +3065,23 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.854701</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.539171</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.5584440000000001</v>
+        <v>0.558818</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.008894000000000001</v>
+        <v>0.019647</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1</v>
@@ -3107,7 +3107,7 @@
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:19.930355Z</t>
+          <t>2026-08-02T15:51:09.199778Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3236,13 +3236,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.854701</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.539171</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3272,27 +3272,31 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
-      <c r="CP7" s="24" t="n"/>
+      <c r="CP7" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>d9a97e5dcb334bb3</t>
+          <t>b2cbb96eafaa44c8</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3302,12 +3306,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3327,26 +3331,26 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-133</v>
+        <v>-223</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.44843</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.690402</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.58052</v>
+        <v>0.703159</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.009705</v>
+        <v>0.012757</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
@@ -3369,7 +3373,7 @@
       <c r="AD8" s="24" t="n"/>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3410,32 +3414,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3453,7 +3457,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3468,7 +3472,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3488,7 +3492,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:22.606056Z</t>
+          <t>2026-08-02T15:51:12.813283Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3498,13 +3502,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-133</v>
+        <v>-223</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.44843</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.690402</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3534,27 +3538,31 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
-      <c r="CP8" s="24" t="n"/>
+      <c r="CP8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>e502908325784a88</t>
+          <t>151bbe4e59ab473a</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3564,12 +3572,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3589,23 +3597,23 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.613497</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.619772</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.703234</v>
+        <v>0.746312</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.012832</v>
+        <v>0.12654</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
@@ -3631,7 +3639,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3672,32 +3680,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3715,7 +3723,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3730,7 +3738,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3750,7 +3758,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:23.605808Z</t>
+          <t>2026-08-02T15:51:13.406755Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3760,13 +3768,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.613497</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.619772</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3796,27 +3804,31 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="n"/>
+      <c r="CP9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>2168ff7cf0e74ae2</t>
+          <t>2422ba6f5077473b</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T15:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3826,12 +3838,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3841,7 +3853,7 @@
       </c>
       <c r="I10" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J10" s="25" t="n"/>
@@ -3851,23 +3863,23 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-170</v>
+        <v>-233</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.429185</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.6997</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.746484</v>
+        <v>0.74664</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.116854</v>
+        <v>0.04694</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>2</v>
@@ -3893,7 +3905,7 @@
       <c r="AD10" s="24" t="n"/>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3934,32 +3946,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3977,7 +3989,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3992,7 +4004,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4012,7 +4024,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:24.188851Z</t>
+          <t>2026-08-02T15:51:13.923521Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4022,13 +4034,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-170</v>
+        <v>-233</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.429185</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.6997</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4058,27 +4070,31 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="n"/>
+      <c r="CP10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>2ba7a93152ac4650</t>
+          <t>3d38a4f365a94293</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-03T20:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4088,12 +4104,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4113,26 +4129,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-233</v>
+        <v>-144</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.694444</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.590164</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.74769</v>
+        <v>0.649674</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.04799</v>
+        <v>0.05951</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4155,7 +4171,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4196,32 +4212,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4239,7 +4255,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4254,7 +4270,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4274,7 +4290,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:24.702936Z</t>
+          <t>2026-08-02T15:51:17.539022Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4284,13 +4300,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-233</v>
+        <v>-144</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.694444</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.590164</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4320,269 +4336,11 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>5cd6021b574a43bf</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>67937</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0.650601</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>0.060437</v>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T12" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH12" s="24" t="n"/>
-      <c r="AI12" s="31" t="n"/>
-      <c r="AJ12" s="31" t="n"/>
-      <c r="AK12" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL12" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM12" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN12" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO12" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP12" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AQ12" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AR12" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AS12" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AT12" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AU12" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AV12" s="24" t="n"/>
-      <c r="AW12" s="24" t="n"/>
-      <c r="AX12" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY12" s="24" t="n"/>
-      <c r="AZ12" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA12" s="24" t="inlineStr">
-        <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
-        </is>
-      </c>
-      <c r="BB12" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC12" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH12" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T13:07:28.257607Z</t>
-        </is>
-      </c>
-      <c r="BI12" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ12" s="25" t="n"/>
-      <c r="BK12" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL12" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM12" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN12" s="28" t="n"/>
-      <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
-      <c r="BS12" s="28" t="n"/>
-      <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
-      <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
-      <c r="BZ12" s="24" t="n"/>
-      <c r="CA12" s="31" t="n"/>
-      <c r="CB12" s="24" t="n"/>
-      <c r="CC12" s="24" t="n"/>
-      <c r="CD12" s="24" t="n"/>
-      <c r="CE12" s="24" t="n"/>
-      <c r="CF12" s="24" t="n"/>
-      <c r="CG12" s="24" t="n"/>
-      <c r="CH12" s="24" t="n"/>
-      <c r="CI12" s="24" t="n"/>
-      <c r="CJ12" s="24" t="n"/>
-      <c r="CK12" s="24" t="n"/>
-      <c r="CL12" s="24" t="n"/>
-      <c r="CM12" s="24" t="n"/>
-      <c r="CN12" s="24" t="n"/>
-      <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="n"/>
+      <c r="CP11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP11" headerRowCount="1">
-  <autoFilter ref="A1:CP11"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ11" headerRowCount="1">
+  <autoFilter ref="A1:CQ11"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP11"/>
+  <dimension ref="A1:CQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,6 +2735,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3011,6 +3022,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3272,7 +3284,8 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
-      <c r="CP7" s="24" t="inlineStr">
+      <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3281,12 +3294,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>b2cbb96eafaa44c8</t>
+          <t>c14fc9f2d16a48d0</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3457,7 +3470,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3472,7 +3485,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3492,7 +3505,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:12.813283Z</t>
+          <t>2026-08-02T16:14:45.283320Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3538,7 +3551,8 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
-      <c r="CP8" s="24" t="inlineStr">
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3547,12 +3561,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>151bbe4e59ab473a</t>
+          <t>df83ccf9de964eb5</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3723,7 +3737,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3738,7 +3752,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3758,7 +3772,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:13.406755Z</t>
+          <t>2026-08-02T16:14:45.864824Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3804,7 +3818,8 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="inlineStr">
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3813,12 +3828,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>2422ba6f5077473b</t>
+          <t>e48526b483064ec6</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3989,7 +4004,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4004,7 +4019,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4024,7 +4039,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:13.923521Z</t>
+          <t>2026-08-02T16:14:46.366525Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4070,7 +4085,8 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="inlineStr">
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4079,12 +4095,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>3d38a4f365a94293</t>
+          <t>e37b88230f234a66</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4255,7 +4271,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4270,7 +4286,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4290,7 +4306,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:17.539022Z</t>
+          <t>2026-08-02T16:14:49.714123Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4336,7 +4352,8 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="inlineStr">
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -3294,12 +3294,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>c14fc9f2d16a48d0</t>
+          <t>3e4847e84b4f42a7</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:45.283320Z</t>
+          <t>2026-08-02T16:53:05.228074Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3561,12 +3561,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>df83ccf9de964eb5</t>
+          <t>fae1fd8b12114e02</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:45.864824Z</t>
+          <t>2026-08-02T16:53:05.711202Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3828,12 +3828,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>e48526b483064ec6</t>
+          <t>931a342a52074e57</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:46.366525Z</t>
+          <t>2026-08-02T16:53:06.165699Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4095,12 +4095,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>e37b88230f234a66</t>
+          <t>139023a3e3174887</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:49.714123Z</t>
+          <t>2026-08-02T16:53:09.518110Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ11" headerRowCount="1">
-  <autoFilter ref="A1:CQ11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ7" headerRowCount="1">
+  <autoFilter ref="A1:CQ7"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$11)</f>
+        <f>COUNTA('Picks'!$A$2:$A$7)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$11,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$11,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")/(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$11)/SUM('Picks'!$BX$2:$BX$11),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$11)</f>
+        <f>SUM('Picks'!$BY$2:$BY$7)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$11,"&lt;&gt;",'Picks'!$AB$2:$AB$11),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$11,'Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ11"/>
+  <dimension ref="A1:CQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3291,1074 +3291,6 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>3e4847e84b4f42a7</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>67511</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N8" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O8" s="28" t="n">
-        <v>0.703159</v>
-      </c>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n">
-        <v>0.012757</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="S8" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U8" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
-      <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH8" s="24" t="n"/>
-      <c r="AI8" s="31" t="n"/>
-      <c r="AJ8" s="31" t="n"/>
-      <c r="AK8" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL8" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN8" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AQ8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AR8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AS8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AT8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AU8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AV8" s="24" t="n"/>
-      <c r="AW8" s="24" t="n"/>
-      <c r="AX8" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY8" s="24" t="n"/>
-      <c r="AZ8" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA8" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB8" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC8" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD8" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG8" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH8" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:05.228074Z</t>
-        </is>
-      </c>
-      <c r="BI8" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ8" s="25" t="n"/>
-      <c r="BK8" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL8" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM8" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN8" s="28" t="n"/>
-      <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
-      <c r="BS8" s="28" t="n"/>
-      <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
-      <c r="BV8" s="29" t="n"/>
-      <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
-      <c r="BZ8" s="24" t="n"/>
-      <c r="CA8" s="31" t="n"/>
-      <c r="CB8" s="24" t="n"/>
-      <c r="CC8" s="24" t="n"/>
-      <c r="CD8" s="24" t="n"/>
-      <c r="CE8" s="24" t="n"/>
-      <c r="CF8" s="24" t="n"/>
-      <c r="CG8" s="24" t="n"/>
-      <c r="CH8" s="24" t="n"/>
-      <c r="CI8" s="24" t="n"/>
-      <c r="CJ8" s="24" t="n"/>
-      <c r="CK8" s="24" t="n"/>
-      <c r="CL8" s="24" t="n"/>
-      <c r="CM8" s="24" t="n"/>
-      <c r="CN8" s="24" t="n"/>
-      <c r="CO8" s="24" t="n"/>
-      <c r="CP8" s="24" t="n"/>
-      <c r="CQ8" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>fae1fd8b12114e02</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>67515</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.746312</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.12654</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>83</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:05.711202Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN9" s="28" t="n"/>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
-      <c r="CB9" s="24" t="n"/>
-      <c r="CC9" s="24" t="n"/>
-      <c r="CD9" s="24" t="n"/>
-      <c r="CE9" s="24" t="n"/>
-      <c r="CF9" s="24" t="n"/>
-      <c r="CG9" s="24" t="n"/>
-      <c r="CH9" s="24" t="n"/>
-      <c r="CI9" s="24" t="n"/>
-      <c r="CJ9" s="24" t="n"/>
-      <c r="CK9" s="24" t="n"/>
-      <c r="CL9" s="24" t="n"/>
-      <c r="CM9" s="24" t="n"/>
-      <c r="CN9" s="24" t="n"/>
-      <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>931a342a52074e57</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>67566</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.74664</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>0.04694</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:06.165699Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN10" s="28" t="n"/>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
-      <c r="CB10" s="24" t="n"/>
-      <c r="CC10" s="24" t="n"/>
-      <c r="CD10" s="24" t="n"/>
-      <c r="CE10" s="24" t="n"/>
-      <c r="CF10" s="24" t="n"/>
-      <c r="CG10" s="24" t="n"/>
-      <c r="CH10" s="24" t="n"/>
-      <c r="CI10" s="24" t="n"/>
-      <c r="CJ10" s="24" t="n"/>
-      <c r="CK10" s="24" t="n"/>
-      <c r="CL10" s="24" t="n"/>
-      <c r="CM10" s="24" t="n"/>
-      <c r="CN10" s="24" t="n"/>
-      <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>139023a3e3174887</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>67937</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.649674</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.05951</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:09.518110Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN11" s="28" t="n"/>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-      <c r="CB11" s="24" t="n"/>
-      <c r="CC11" s="24" t="n"/>
-      <c r="CD11" s="24" t="n"/>
-      <c r="CE11" s="24" t="n"/>
-      <c r="CF11" s="24" t="n"/>
-      <c r="CG11" s="24" t="n"/>
-      <c r="CH11" s="24" t="n"/>
-      <c r="CI11" s="24" t="n"/>
-      <c r="CJ11" s="24" t="n"/>
-      <c r="CK11" s="24" t="n"/>
-      <c r="CL11" s="24" t="n"/>
-      <c r="CM11" s="24" t="n"/>
-      <c r="CN11" s="24" t="n"/>
-      <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ7" headerRowCount="1">
-  <autoFilter ref="A1:CQ7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ11" headerRowCount="1">
+  <autoFilter ref="A1:CQ11"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$7)</f>
+        <f>COUNTA('Picks'!$A$2:$A$11)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$11,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$11,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")/(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$11)/SUM('Picks'!$BX$2:$BX$11),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$7)</f>
+        <f>SUM('Picks'!$BY$2:$BY$11)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$11,"&lt;&gt;",'Picks'!$AB$2:$AB$11),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$11,'Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ7"/>
+  <dimension ref="A1:CQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3105,18 +3105,38 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="Z7" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC7" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:34:59.847525Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
@@ -3259,8 +3279,12 @@
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="28" t="n"/>
+      <c r="BQ7" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR7" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
       <c r="BU7" s="25" t="n"/>
@@ -3291,6 +3315,1074 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>77bed3ede10b48c3</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.012908</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.281478Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>5783b911c4ee4756</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.746406</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.137031</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.851259Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>c6673aa0176b412e</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.746125</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.046425</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:18.386531Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>e287ebe2b5fc432b</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.649195</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.059031</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:21.959634Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -3318,12 +3318,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>77bed3ede10b48c3</t>
+          <t>93e6957068f54f9a</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:17.281478Z</t>
+          <t>2026-08-02T18:12:18.085863Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3585,12 +3585,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>5783b911c4ee4756</t>
+          <t>44df308626db4f59</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:17.851259Z</t>
+          <t>2026-08-02T18:12:18.584911Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>c6673aa0176b412e</t>
+          <t>2620d69bf9fa4526</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:18.386531Z</t>
+          <t>2026-08-02T18:12:19.163906Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4119,12 +4119,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>e287ebe2b5fc432b</t>
+          <t>7d592c48ea8e4cbd</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:21.959634Z</t>
+          <t>2026-08-02T18:12:22.895388Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ11" headerRowCount="1">
-  <autoFilter ref="A1:CQ11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ7" headerRowCount="1">
+  <autoFilter ref="A1:CQ7"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$11)</f>
+        <f>COUNTA('Picks'!$A$2:$A$7)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$11,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$11,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")/(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$11)/SUM('Picks'!$BX$2:$BX$11),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$11)</f>
+        <f>SUM('Picks'!$BY$2:$BY$7)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$11,"&lt;&gt;",'Picks'!$AB$2:$AB$11),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$11,'Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ11"/>
+  <dimension ref="A1:CQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3315,1074 +3315,6 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>93e6957068f54f9a</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>67511</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N8" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O8" s="28" t="n">
-        <v>0.70331</v>
-      </c>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n">
-        <v>0.012908</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="S8" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U8" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
-      <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH8" s="24" t="n"/>
-      <c r="AI8" s="31" t="n"/>
-      <c r="AJ8" s="31" t="n"/>
-      <c r="AK8" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL8" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN8" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AQ8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AR8" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AS8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AT8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AU8" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AV8" s="24" t="n"/>
-      <c r="AW8" s="24" t="n"/>
-      <c r="AX8" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY8" s="24" t="n"/>
-      <c r="AZ8" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA8" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB8" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC8" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD8" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG8" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH8" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:18.085863Z</t>
-        </is>
-      </c>
-      <c r="BI8" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ8" s="25" t="n"/>
-      <c r="BK8" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL8" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM8" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN8" s="28" t="n"/>
-      <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
-      <c r="BS8" s="28" t="n"/>
-      <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
-      <c r="BV8" s="29" t="n"/>
-      <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
-      <c r="BZ8" s="24" t="n"/>
-      <c r="CA8" s="31" t="n"/>
-      <c r="CB8" s="24" t="n"/>
-      <c r="CC8" s="24" t="n"/>
-      <c r="CD8" s="24" t="n"/>
-      <c r="CE8" s="24" t="n"/>
-      <c r="CF8" s="24" t="n"/>
-      <c r="CG8" s="24" t="n"/>
-      <c r="CH8" s="24" t="n"/>
-      <c r="CI8" s="24" t="n"/>
-      <c r="CJ8" s="24" t="n"/>
-      <c r="CK8" s="24" t="n"/>
-      <c r="CL8" s="24" t="n"/>
-      <c r="CM8" s="24" t="n"/>
-      <c r="CN8" s="24" t="n"/>
-      <c r="CO8" s="24" t="n"/>
-      <c r="CP8" s="24" t="n"/>
-      <c r="CQ8" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>44df308626db4f59</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>67515</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.746406</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.137031</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>89</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:18.584911Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN9" s="28" t="n"/>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
-      <c r="CB9" s="24" t="n"/>
-      <c r="CC9" s="24" t="n"/>
-      <c r="CD9" s="24" t="n"/>
-      <c r="CE9" s="24" t="n"/>
-      <c r="CF9" s="24" t="n"/>
-      <c r="CG9" s="24" t="n"/>
-      <c r="CH9" s="24" t="n"/>
-      <c r="CI9" s="24" t="n"/>
-      <c r="CJ9" s="24" t="n"/>
-      <c r="CK9" s="24" t="n"/>
-      <c r="CL9" s="24" t="n"/>
-      <c r="CM9" s="24" t="n"/>
-      <c r="CN9" s="24" t="n"/>
-      <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>2620d69bf9fa4526</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>67566</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.746125</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>0.046425</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:19.163906Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN10" s="28" t="n"/>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
-      <c r="CB10" s="24" t="n"/>
-      <c r="CC10" s="24" t="n"/>
-      <c r="CD10" s="24" t="n"/>
-      <c r="CE10" s="24" t="n"/>
-      <c r="CF10" s="24" t="n"/>
-      <c r="CG10" s="24" t="n"/>
-      <c r="CH10" s="24" t="n"/>
-      <c r="CI10" s="24" t="n"/>
-      <c r="CJ10" s="24" t="n"/>
-      <c r="CK10" s="24" t="n"/>
-      <c r="CL10" s="24" t="n"/>
-      <c r="CM10" s="24" t="n"/>
-      <c r="CN10" s="24" t="n"/>
-      <c r="CO10" s="24" t="n"/>
-      <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>7d592c48ea8e4cbd</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>67937</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.649195</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.059031</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:22.895388Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN11" s="28" t="n"/>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-      <c r="CB11" s="24" t="n"/>
-      <c r="CC11" s="24" t="n"/>
-      <c r="CD11" s="24" t="n"/>
-      <c r="CE11" s="24" t="n"/>
-      <c r="CF11" s="24" t="n"/>
-      <c r="CG11" s="24" t="n"/>
-      <c r="CH11" s="24" t="n"/>
-      <c r="CI11" s="24" t="n"/>
-      <c r="CJ11" s="24" t="n"/>
-      <c r="CK11" s="24" t="n"/>
-      <c r="CL11" s="24" t="n"/>
-      <c r="CM11" s="24" t="n"/>
-      <c r="CN11" s="24" t="n"/>
-      <c r="CO11" s="24" t="n"/>
-      <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ7" headerRowCount="1">
-  <autoFilter ref="A1:CQ7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ11" headerRowCount="1">
+  <autoFilter ref="A1:CQ11"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$7)</f>
+        <f>COUNTA('Picks'!$A$2:$A$11)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$11,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$11,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")/(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$11)/SUM('Picks'!$BX$2:$BX$11),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$7)</f>
+        <f>SUM('Picks'!$BY$2:$BY$11)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$11,"&lt;&gt;",'Picks'!$AB$2:$AB$11),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$11,'Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ7"/>
+  <dimension ref="A1:CQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3315,6 +3315,1074 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>aca2ade9d954416d</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.012908</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.781954Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>087baf390a764e55</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.746406</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.137031</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.279453Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>6321f5b533cc49d7</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.746125</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.046425</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.786284Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>d0dab6b96b4946b2</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.649195</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.059031</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.243617Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ11" headerRowCount="1">
-  <autoFilter ref="A1:CQ11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
+  <autoFilter ref="A1:CQ18"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$11)</f>
+        <f>COUNTA('Picks'!$A$2:$A$18)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$11,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$11,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")/(COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"win")+COUNTIFS('Picks'!$BX$2:$BX$11,"&gt;0",'Picks'!$V$2:$V$11,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$11)/SUM('Picks'!$BX$2:$BX$11),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$11)</f>
+        <f>SUM('Picks'!$BY$2:$BY$18)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$11,"&lt;&gt;",'Picks'!$AB$2:$AB$11),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$11,'Picks'!$AM$2:$AM$11,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A14,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A15,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled",'Picks'!$V$2:$V$11,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$11,'Picks'!$H$2:$H$11,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$11,'Picks'!$H$2:$H$11,$A16,'Picks'!$U$2:$U$11,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ11"/>
+  <dimension ref="A1:CQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3318,12 +3318,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>aca2ade9d954416d</t>
+          <t>55b34ffe3b5d4fe1</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T06:30:34.654651Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3368,23 +3368,23 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-223</v>
+        <v>-170</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.588235</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.62963</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.70331</v>
+        <v>0.703892</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.012908</v>
+        <v>0.07426199999999999</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>2</v>
@@ -3396,21 +3396,41 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="Z8" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC8" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:27:36.882808Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3420,7 +3440,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3494,7 +3514,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3509,7 +3529,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3529,7 +3549,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:09.781954Z</t>
+          <t>2026-08-03T06:30:13.245481Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3539,19 +3559,23 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-223</v>
+        <v>-170</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.588235</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.62963</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
+      <c r="BQ8" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR8" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
       <c r="BU8" s="25" t="n"/>
@@ -3585,22 +3609,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>087baf390a764e55</t>
+          <t>1d9cd56d3c7b4494</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T13:30:58.881408Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T15:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3610,12 +3634,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3625,7 +3649,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J9" s="25" t="n"/>
@@ -3635,23 +3659,23 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.746406</v>
+        <v>0.745478</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.137031</v>
+        <v>0.055076</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
@@ -3663,21 +3687,41 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="Z9" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC9" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:48:25.231418Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3718,32 +3762,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3761,7 +3805,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3776,7 +3820,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3796,7 +3840,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:10.279453Z</t>
+          <t>2026-08-03T13:30:33.645010Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3806,19 +3850,23 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
       <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
+      <c r="BQ9" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR9" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
       <c r="BU9" s="25" t="n"/>
@@ -3852,22 +3900,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>6321f5b533cc49d7</t>
+          <t>919f9bf38a784742</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T17:09:03.086605Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-03T19:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>63451</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3877,12 +3925,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3892,7 +3940,7 @@
       </c>
       <c r="I10" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J10" s="25" t="n"/>
@@ -3902,23 +3950,23 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.44843</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.690402</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.746125</v>
+        <v>0.727674</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.046425</v>
+        <v>0.037272</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>2</v>
@@ -3930,21 +3978,41 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="Z10" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC10" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:17.207636Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tse-vksa-2026-07-30).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3954,7 +4022,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -3985,32 +4053,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -4028,7 +4096,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4043,7 +4111,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4063,7 +4131,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:10.786284Z</t>
+          <t>2026-08-03T17:08:43.723243Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4073,19 +4141,23 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.44843</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.690402</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
       <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
+      <c r="BQ10" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR10" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
       <c r="BU10" s="25" t="n"/>
@@ -4119,22 +4191,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>d0dab6b96b4946b2</t>
+          <t>d2515bfa54a74d5f</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-04T02:00:56.302645Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00Z</t>
+          <t>2026-08-04T15:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>70566</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4144,12 +4216,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Barcząca Esports</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Lodis</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4159,7 +4231,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4169,26 +4241,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-144</v>
+        <v>223</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.694444</v>
+        <v>3.23</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.309598</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.649195</v>
+        <v>0.69409</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.059031</v>
+        <v>0.384492</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4211,7 +4283,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-lol-lds-bce-2026-08-04).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4252,32 +4324,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Barcząca Esports</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Barcząca Esports</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Barcząca Esports</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Lodis</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Lodis</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Lodis</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4295,7 +4367,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4310,7 +4382,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4330,7 +4402,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:14.243617Z</t>
+          <t>2026-08-04T02:00:43.286617Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4340,13 +4412,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-144</v>
+        <v>223</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.694444</v>
+        <v>3.23</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.309598</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4383,6 +4455,1875 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>b6d267763de14a95</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.631317</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.121513</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:44.932625Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>7aa2d8ba6e944aab</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>68689</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.5739340000000001</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.003119</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:48.567590Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>a499fd2d6bc242b4</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:49.613554Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>6e8643739e154f97</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.624143</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.004371</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:52.417381Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>c3cba5c251004ed2</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.591618</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.032147</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:53.026230Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>6dfc92e9643446e9</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.604656</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.004656</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:55.187744Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>8e5dc7d15614471b</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>69336</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.74222</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.072253</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-est-nerd-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.301588Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ18" headerRowCount="1">
-  <autoFilter ref="A1:CQ18"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR27" headerRowCount="1">
+  <autoFilter ref="A1:CR27"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$18)</f>
+        <f>COUNTA('Picks'!$A$2:$A$27)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$18)</f>
+        <f>SUM('Picks'!$BY$2:$BY$27)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CR27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3023,6 +3034,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3309,7 +3321,8 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
-      <c r="CQ7" s="24" t="inlineStr">
+      <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3600,7 +3613,8 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
-      <c r="CQ8" s="24" t="inlineStr">
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3891,7 +3905,8 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4182,7 +4197,8 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4191,22 +4207,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>d2515bfa54a74d5f</t>
+          <t>cd19577b75be4ba2</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T15:00:00Z</t>
+          <t>2026-08-04T16:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>70566</t>
+          <t>68509</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4216,12 +4232,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4231,7 +4247,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4241,26 +4257,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>223</v>
+        <v>-108</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>3.23</v>
+        <v>1.925926</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.519231</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.69409</v>
+        <v>0.631317</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.384492</v>
+        <v>0.112086</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4283,7 +4299,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-lol-lds-bce-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4324,32 +4340,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4367,7 +4383,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4382,7 +4398,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4402,7 +4418,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:43.286617Z</t>
+          <t>2026-08-04T08:56:25.701342Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4412,13 +4428,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>223</v>
+        <v>-108</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>3.23</v>
+        <v>1.925926</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.519231</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4449,7 +4465,8 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4458,22 +4475,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>b6d267763de14a95</t>
+          <t>e07416f652a943fe</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:00:00Z</t>
+          <t>2026-08-04T18:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>68509</t>
+          <t>68690</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4483,12 +4500,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4508,26 +4525,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.854701</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.539171</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.631317</v>
+        <v>0.55055</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.121513</v>
+        <v>0.011379</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4550,7 +4567,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4591,32 +4608,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4634,7 +4651,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4649,7 +4666,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4669,7 +4686,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:44.932625Z</t>
+          <t>2026-08-04T08:56:29.939077Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4679,13 +4696,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.854701</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.539171</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4716,7 +4733,8 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4725,22 +4743,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>7aa2d8ba6e944aab</t>
+          <t>b49970048ce545a2</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00Z</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>68689</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4750,12 +4768,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4775,26 +4793,26 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-133</v>
+        <v>-163</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.613497</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.619772</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.5739340000000001</v>
+        <v>0.624143</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.003119</v>
+        <v>0.004371</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>22</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
@@ -4817,7 +4835,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4858,32 +4876,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4901,7 +4919,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4916,7 +4934,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4936,7 +4954,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:48.567590Z</t>
+          <t>2026-08-04T08:56:34.284466Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4946,13 +4964,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-133</v>
+        <v>-163</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.613497</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.619772</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4983,7 +5001,8 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4992,22 +5011,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>a499fd2d6bc242b4</t>
+          <t>047b74a1590e4046</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00Z</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>68690</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5017,12 +5036,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5042,26 +5061,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-122</v>
+        <v>104</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.04</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.490196</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.55055</v>
+        <v>0.591618</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.001</v>
+        <v>0.101422</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5084,7 +5103,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5125,32 +5144,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5168,7 +5187,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5183,7 +5202,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5203,7 +5222,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:49.613554Z</t>
+          <t>2026-08-04T08:56:34.823771Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5213,13 +5232,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-122</v>
+        <v>104</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.04</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.490196</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5250,7 +5269,8 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5259,22 +5279,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>6e8643739e154f97</t>
+          <t>8b18a86d7c0d4355</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T21:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5284,12 +5304,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5309,26 +5329,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-163</v>
+        <v>194</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.94</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.340136</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.624143</v>
+        <v>0.5725</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.004371</v>
+        <v>0.232364</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5351,7 +5371,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5392,32 +5412,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5435,7 +5455,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5450,7 +5470,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5470,7 +5490,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:52.417381Z</t>
+          <t>2026-08-04T08:56:36.567095Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5480,13 +5500,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-163</v>
+        <v>194</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.94</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.340136</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5517,7 +5537,8 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5526,22 +5547,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>c3cba5c251004ed2</t>
+          <t>116b7c250ff34309</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T22:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>69273</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5551,12 +5572,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5576,23 +5597,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-127</v>
+        <v>-117</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.854701</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.539171</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.591618</v>
+        <v>0.604656</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.032147</v>
+        <v>0.065485</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1.25</v>
@@ -5618,7 +5639,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5659,32 +5680,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5702,7 +5723,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5717,7 +5738,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5737,7 +5758,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:53.026230Z</t>
+          <t>2026-08-04T08:56:37.194950Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5747,13 +5768,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-127</v>
+        <v>-117</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.854701</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.539171</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5784,7 +5805,8 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5793,22 +5815,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>6dfc92e9643446e9</t>
+          <t>b9bf217f151d4091</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:00:00Z</t>
+          <t>2026-08-05T05:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>69273</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5818,12 +5840,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5843,26 +5865,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.724638</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.6</v>
+        <v>0.579832</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.604656</v>
+        <v>0.638913</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.004656</v>
+        <v>0.059081</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5885,7 +5907,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-dkc-nsea-2026-08-05).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5926,32 +5948,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5969,7 +5991,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5984,7 +6006,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6004,7 +6026,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:55.187744Z</t>
+          <t>2026-08-04T08:56:38.863908Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6014,13 +6036,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.724638</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.6</v>
+        <v>0.579832</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -6051,7 +6073,8 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6060,22 +6083,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>8e5dc7d15614471b</t>
+          <t>9a06f18321044d68</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:00:00Z</t>
+          <t>2026-08-05T08:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>69512</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6085,12 +6108,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6100,7 +6123,7 @@
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J18" s="25" t="n"/>
@@ -6110,23 +6133,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-203</v>
+        <v>-223</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.44843</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.690402</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.74222</v>
+        <v>0.739915</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.072253</v>
+        <v>0.049513</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>2</v>
@@ -6152,7 +6175,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-est-nerd-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6193,32 +6216,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6236,7 +6259,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6251,7 +6274,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6271,7 +6294,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.301588Z</t>
+          <t>2026-08-04T08:56:39.828051Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6281,13 +6304,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-203</v>
+        <v>-223</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.44843</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.690402</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6318,7 +6341,2420 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>fbb234a2434a4bdd</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.699554</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.090179</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:40.294698Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>59c3c652dafb40a8</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.637225</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.077754</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:41.252699Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>cc0291a39c6a424f</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.665588</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.045816</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-tlnp-gal-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:44.546269Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>91ae9ef4ef004b3d</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.561203</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.120674</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.445811Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>59a9fb58824e49de</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.832591</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.242427</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.442405Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>832fdf28574146a0</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.577055</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.077055</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.949141Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>8043fd64f6b74293</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.607498</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.088267</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:51.809850Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>0b03902ebfa24b4d</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.5668840000000001</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.137699</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:54.874184Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>8e329600fabb40f0</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.590765</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469425Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR27" headerRowCount="1">
-  <autoFilter ref="A1:CR27"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS27" headerRowCount="1">
+  <autoFilter ref="A1:CS27"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR27"/>
+  <dimension ref="A1:CS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3035,6 +3046,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3322,7 +3334,8 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
-      <c r="CR7" s="24" t="inlineStr">
+      <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3614,7 +3627,8 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
-      <c r="CR8" s="24" t="inlineStr">
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3906,7 +3920,8 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
-      <c r="CR9" s="24" t="inlineStr">
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4198,7 +4213,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4207,12 +4223,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>cd19577b75be4ba2</t>
+          <t>de23af83867246d1</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4257,23 +4273,23 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-108</v>
+        <v>-138</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.724638</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.579832</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.631317</v>
+        <v>0.631258</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.112086</v>
+        <v>0.051426</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>1.5</v>
@@ -4299,7 +4315,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4383,7 +4399,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4398,7 +4414,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4418,7 +4434,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:25.701342Z</t>
+          <t>2026-08-04T14:26:42.602034Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4428,13 +4444,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-108</v>
+        <v>-138</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.724638</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.579832</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4466,7 +4482,8 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
-      <c r="CR11" s="24" t="inlineStr">
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4475,12 +4492,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>e07416f652a943fe</t>
+          <t>99f2963d09cd4500</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4534,11 +4551,11 @@
         <v>0.539171</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.55055</v>
+        <v>0.5509500000000001</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.011379</v>
+        <v>0.011779</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>26</v>
@@ -4651,7 +4668,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4666,7 +4683,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4686,7 +4703,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:29.939077Z</t>
+          <t>2026-08-04T14:26:46.197810Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4734,7 +4751,8 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
-      <c r="CR12" s="24" t="inlineStr">
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4743,12 +4761,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>b49970048ce545a2</t>
+          <t>3e10310dcbf04ce3</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4802,11 +4820,11 @@
         <v>0.619772</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.624143</v>
+        <v>0.624122</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.004371</v>
+        <v>0.00435</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>22</v>
@@ -4919,7 +4937,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4934,7 +4952,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4954,7 +4972,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:34.284466Z</t>
+          <t>2026-08-04T14:26:50.250119Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -5002,7 +5020,8 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
-      <c r="CR13" s="24" t="inlineStr">
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5011,12 +5030,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>047b74a1590e4046</t>
+          <t>7bd45d10fbc242ff</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5061,23 +5080,23 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.460829</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.591618</v>
+        <v>0.5918</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.101422</v>
+        <v>0.130971</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>1.25</v>
@@ -5103,7 +5122,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5187,7 +5206,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5202,7 +5221,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5222,7 +5241,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:34.823771Z</t>
+          <t>2026-08-04T14:26:50.876512Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5232,13 +5251,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.460829</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5270,7 +5289,8 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5279,12 +5299,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>8b18a86d7c0d4355</t>
+          <t>b8480a62093548bf</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5329,20 +5349,20 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.330033</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.5725</v>
+        <v>0.572751</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.232364</v>
+        <v>0.242718</v>
       </c>
       <c r="R15" s="26" t="n">
         <v>100</v>
@@ -5371,7 +5391,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5455,7 +5475,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5470,7 +5490,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5490,7 +5510,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:36.567095Z</t>
+          <t>2026-08-04T14:26:52.692865Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5500,13 +5520,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.330033</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5538,7 +5558,8 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
-      <c r="CR15" s="24" t="inlineStr">
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5547,12 +5568,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>116b7c250ff34309</t>
+          <t>bb0e3fcaa8894fc8</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5597,23 +5618,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.884956</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.530516</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.604656</v>
+        <v>0.604693</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.065485</v>
+        <v>0.07417700000000001</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1.25</v>
@@ -5639,7 +5660,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5723,7 +5744,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5738,7 +5759,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5758,7 +5779,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:37.194950Z</t>
+          <t>2026-08-04T14:26:53.902256Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5768,13 +5789,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.884956</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.530516</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5806,7 +5827,8 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
-      <c r="CR16" s="24" t="inlineStr">
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5815,12 +5837,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>b9bf217f151d4091</t>
+          <t>55442dc4c7b945ac</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5874,14 +5896,14 @@
         <v>0.579832</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.638913</v>
+        <v>0.638652</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.059081</v>
+        <v>0.05882</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>1.5</v>
@@ -5991,7 +6013,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -6006,7 +6028,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6026,7 +6048,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:38.863908Z</t>
+          <t>2026-08-04T14:26:56.319431Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6074,7 +6096,8 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6083,12 +6106,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>9a06f18321044d68</t>
+          <t>f163e67427c04456</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6098,7 +6121,7 @@
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>69512</t>
+          <t>69511</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6108,12 +6131,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6123,7 +6146,7 @@
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J18" s="25" t="n"/>
@@ -6133,23 +6156,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-223</v>
+        <v>-186</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.537634</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.65035</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.739915</v>
+        <v>0.699121</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.049513</v>
+        <v>0.048771</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>2</v>
@@ -6175,7 +6198,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6216,32 +6239,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6259,7 +6282,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6274,7 +6297,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6294,7 +6317,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:39.828051Z</t>
+          <t>2026-08-04T14:26:56.857793Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6304,13 +6327,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-223</v>
+        <v>-186</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.537634</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.65035</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6342,7 +6365,8 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6351,12 +6375,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>fbb234a2434a4bdd</t>
+          <t>91f1a623718e470b</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6366,7 +6390,7 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>69512</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6376,12 +6400,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6391,7 +6415,7 @@
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J19" s="25" t="n"/>
@@ -6401,23 +6425,23 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.699554</v>
+        <v>0.752668</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.090179</v>
+        <v>0.062266</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>2</v>
@@ -6443,7 +6467,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6484,32 +6508,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6527,7 +6551,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6542,7 +6566,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6562,7 +6586,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:40.294698Z</t>
+          <t>2026-08-04T14:26:57.357254Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6572,13 +6596,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6610,7 +6634,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6619,12 +6644,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>59c3c652dafb40a8</t>
+          <t>a5e2f150278e4bf1</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6669,26 +6694,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.637225</v>
+        <v>0.6034</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.077754</v>
+        <v>0.05385</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6711,7 +6736,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6795,7 +6820,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6810,7 +6835,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6830,7 +6855,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:41.252699Z</t>
+          <t>2026-08-04T14:26:58.482445Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6840,13 +6865,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6878,7 +6903,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6887,22 +6913,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>cc0291a39c6a424f</t>
+          <t>df9b9919858d4118</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:00:00Z</t>
+          <t>2026-08-05T17:00:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6912,12 +6938,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6927,7 +6953,7 @@
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J21" s="25" t="n"/>
@@ -6937,26 +6963,26 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-163</v>
+        <v>-144</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.694444</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.590164</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.665588</v>
+        <v>0.831719</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.045816</v>
+        <v>0.241555</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -6979,7 +7005,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-tlnp-gal-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7020,32 +7046,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7063,7 +7089,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7078,7 +7104,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7098,7 +7124,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:44.546269Z</t>
+          <t>2026-08-04T14:27:04.870108Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7108,13 +7134,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-163</v>
+        <v>-144</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.694444</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.590164</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7146,7 +7172,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7155,12 +7182,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>91ae9ef4ef004b3d</t>
+          <t>fff580890c974e17</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7214,14 +7241,14 @@
         <v>0.440529</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.561203</v>
+        <v>0.56154</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.120674</v>
+        <v>0.121011</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
@@ -7331,7 +7358,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7346,7 +7373,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7366,7 +7393,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:46.445811Z</t>
+          <t>2026-08-04T14:27:05.368556Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7414,7 +7441,8 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7423,22 +7451,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>59a9fb58824e49de</t>
+          <t>901e41bf638b485d</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:00:00Z</t>
+          <t>2026-08-05T17:30:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7448,12 +7476,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7473,26 +7501,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.694444</v>
+        <v>2</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.832591</v>
+        <v>0.577308</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.242427</v>
+        <v>0.077308</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7515,7 +7543,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7556,32 +7584,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7599,7 +7627,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7614,7 +7642,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7634,7 +7662,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:47.442405Z</t>
+          <t>2026-08-04T14:27:06.503337Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7644,13 +7672,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.694444</v>
+        <v>2</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7682,7 +7710,8 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7691,22 +7720,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>832fdf28574146a0</t>
+          <t>cb80a5f81d224a54</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:30:00Z</t>
+          <t>2026-08-05T19:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>69931</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7716,12 +7745,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7731,7 +7760,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -7741,26 +7770,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>100</v>
+        <v>-127</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2</v>
+        <v>1.787402</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.5</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.577055</v>
+        <v>0.606257</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.077055</v>
+        <v>0.046786</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -7783,7 +7812,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7824,32 +7853,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -7867,7 +7896,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7882,7 +7911,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7902,7 +7931,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:47.949141Z</t>
+          <t>2026-08-04T14:27:11.034551Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7912,13 +7941,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>100</v>
+        <v>-127</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>2</v>
+        <v>1.787402</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.5</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -7950,7 +7979,8 @@
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
-      <c r="CR24" s="24" t="inlineStr">
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7959,22 +7989,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>8043fd64f6b74293</t>
+          <t>32b70f3637ee4af5</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00:00Z</t>
+          <t>2026-08-05T20:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>70301</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -7984,12 +8014,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -7999,7 +8029,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8009,26 +8039,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.925926</v>
+        <v>2</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.5</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.607498</v>
+        <v>0.658341</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.088267</v>
+        <v>0.158341</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8051,7 +8081,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8092,32 +8122,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8135,7 +8165,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8150,7 +8180,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8170,7 +8200,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:51.809850Z</t>
+          <t>2026-08-04T14:27:11.579319Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8180,13 +8210,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.925926</v>
+        <v>2</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.5</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8218,7 +8248,8 @@
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
-      <c r="CR25" s="24" t="inlineStr">
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8227,12 +8258,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>0b03902ebfa24b4d</t>
+          <t>b0c191ce7ce345d3</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8277,23 +8308,23 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.45045</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.5668840000000001</v>
+        <v>0.565806</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.137699</v>
+        <v>0.115356</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>1</v>
@@ -8319,7 +8350,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8403,7 +8434,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8418,7 +8449,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8438,7 +8469,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:54.874184Z</t>
+          <t>2026-08-04T14:27:14.606628Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8448,13 +8479,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.45045</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8486,7 +8517,8 @@
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
-      <c r="CR26" s="24" t="inlineStr">
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8495,12 +8527,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>8e329600fabb40f0</t>
+          <t>3baeb1b9f3814ddc</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8554,14 +8586,14 @@
         <v>0.570815</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.590765</v>
+        <v>0.589642</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.01995</v>
+        <v>0.018827</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1.25</v>
@@ -8671,7 +8703,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8686,7 +8718,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8706,7 +8738,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469425Z</t>
+          <t>2026-08-04T14:27:16.243697Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8754,7 +8786,8 @@
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
-      <c r="CR27" s="24" t="inlineStr">
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS27" headerRowCount="1">
-  <autoFilter ref="A1:CS27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS37" headerRowCount="1">
+  <autoFilter ref="A1:CS37"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$27)</f>
+        <f>COUNTA('Picks'!$A$2:$A$37)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$27)</f>
+        <f>SUM('Picks'!$BY$2:$BY$37)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS27"/>
+  <dimension ref="A1:CS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4223,12 +4223,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>de23af83867246d1</t>
+          <t>be2db88654a24a40</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T15:04:56.339784Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4301,18 +4301,38 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC11" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:51.571209Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
@@ -4325,7 +4345,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4399,7 +4419,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>70926375efdbac84dce8c51337c5a10529e7ee005d64ab556a8536dd0bdf8d2f</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4414,7 +4434,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>70926375efdbac84dce8c51337c5a10529e7ee005d64ab556a8536dd0bdf8d2f</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4434,7 +4454,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:42.602034Z</t>
+          <t>2026-08-04T15:04:19.459782Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4455,8 +4475,12 @@
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
       <c r="BU11" s="25" t="n"/>
@@ -4492,12 +4516,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>99f2963d09cd4500</t>
+          <t>e7b27a6351004271</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T16:54:52.896251Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4507,7 +4531,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>68690</t>
+          <t>68688</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4517,12 +4541,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4532,7 +4556,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4542,49 +4566,69 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.5509500000000001</v>
+        <v>0.530674</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.011779</v>
+        <v>0.02087</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:06.736199Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-zyb-jl-2026-08-04).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4625,32 +4669,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4668,7 +4712,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>5bcf4e232e6e233164ffd78633a5487d986e0433e7ea70b93f7ff1c53933694d</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4678,12 +4722,12 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>5bcf4e232e6e233164ffd78633a5487d986e0433e7ea70b93f7ff1c53933694d</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4698,12 +4742,12 @@
       </c>
       <c r="BG12" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:46.197810Z</t>
+          <t>2026-08-04T16:54:19.630031Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4713,19 +4757,23 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -4761,12 +4809,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>3e10310dcbf04ce3</t>
+          <t>3f74d898ac9646d8</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T18:08:50.279200Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4776,7 +4824,7 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4786,12 +4834,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4811,49 +4859,69 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-163</v>
+        <v>122</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.22</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.45045</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.624122</v>
+        <v>0.56541</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.00435</v>
+        <v>0.11496</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="Z13" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC13" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:08.029029Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4863,7 +4931,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4894,32 +4962,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4937,7 +5005,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4947,12 +5015,12 @@
       </c>
       <c r="BC13" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4967,12 +5035,12 @@
       </c>
       <c r="BG13" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:50.250119Z</t>
+          <t>2026-08-04T18:08:14.538966Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4982,19 +5050,23 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-163</v>
+        <v>122</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.22</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.45045</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
+      <c r="BQ13" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR13" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
       <c r="BU13" s="25" t="n"/>
@@ -5030,12 +5102,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>7bd45d10fbc242ff</t>
+          <t>826e1c0eddf0473f</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T18:08:50.279200Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5045,7 +5117,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5055,12 +5127,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5080,49 +5152,69 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>117</v>
+        <v>-194</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.17</v>
+        <v>1.515464</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.659864</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.5918</v>
+        <v>0.663313</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.130971</v>
+        <v>0.003449</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="AC14" s="30" t="n">
+        <v>0.9021</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:09.282327Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-kcb-vitb-2026-08-04).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5163,32 +5255,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5206,7 +5298,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5216,12 +5308,12 @@
       </c>
       <c r="BC14" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5236,12 +5328,12 @@
       </c>
       <c r="BG14" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:50.876512Z</t>
+          <t>2026-08-04T18:08:15.286337Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5251,19 +5343,23 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>117</v>
+        <v>-194</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.17</v>
+        <v>1.515464</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.659864</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5299,12 +5395,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>b8480a62093548bf</t>
+          <t>e87b40da89ed44aa</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T18:08:50.279200Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5358,37 +5454,57 @@
         <v>0.330033</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.572751</v>
+        <v>0.552115</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.242718</v>
+        <v>0.222082</v>
       </c>
       <c r="R15" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>-3.3e-05</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:40.231508Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
@@ -5401,7 +5517,7 @@
       </c>
       <c r="AG15" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH15" s="24" t="n"/>
@@ -5475,7 +5591,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5485,12 +5601,12 @@
       </c>
       <c r="BC15" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5505,12 +5621,12 @@
       </c>
       <c r="BG15" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:52.692865Z</t>
+          <t>2026-08-04T18:08:16.814975Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5531,8 +5647,12 @@
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.33</v>
+      </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5568,12 +5688,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>bb0e3fcaa8894fc8</t>
+          <t>74ff8cb85b6c4687</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T18:08:50.279200Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5627,37 +5747,57 @@
         <v>0.530516</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.604693</v>
+        <v>0.610688</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.07417700000000001</v>
+        <v>0.08017199999999999</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>1.3274</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:42.280534Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
@@ -5744,7 +5884,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5754,12 +5894,12 @@
       </c>
       <c r="BC16" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>581bb511aff842f9af01d132a2c739b65878388c9d1d8f1182f28b3c271e9a2c</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5774,12 +5914,12 @@
       </c>
       <c r="BG16" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:53.902256Z</t>
+          <t>2026-08-04T18:08:17.591273Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5800,8 +5940,12 @@
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -5837,22 +5981,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>55442dc4c7b945ac</t>
+          <t>3e2ddc0f60084cb5</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-04T22:03:07.434111Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T05:00:00Z</t>
+          <t>2026-08-04T23:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>69507</t>
+          <t>69304</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5862,12 +6006,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5877,7 +6021,7 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J17" s="25" t="n"/>
@@ -5887,49 +6031,69 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-138</v>
+        <v>-117</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.854701</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.539171</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.638652</v>
+        <v>0.542093</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.05882</v>
+        <v>0.002922</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:44.159759Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-dkc-nsea-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-kbm-pnga-2026-08-04).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5939,7 +6103,7 @@
       </c>
       <c r="AG17" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH17" s="24" t="n"/>
@@ -5970,32 +6134,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -6013,7 +6177,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>97b6e7d388d98e9492a794fb2cdef05114fd516a988a71f95285158326a46434</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -6023,12 +6187,12 @@
       </c>
       <c r="BC17" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>97b6e7d388d98e9492a794fb2cdef05114fd516a988a71f95285158326a46434</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6043,12 +6207,12 @@
       </c>
       <c r="BG17" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:56.319431Z</t>
+          <t>2026-08-04T22:02:38.695907Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6058,19 +6222,23 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-138</v>
+        <v>-117</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.854701</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.539171</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6106,22 +6274,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>f163e67427c04456</t>
+          <t>2ed3a33fa9b847a4</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T08:00:00Z</t>
+          <t>2026-08-05T05:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6131,12 +6299,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6156,30 +6324,30 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-186</v>
+        <v>-104</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.961538</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.509804</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.699121</v>
+        <v>0.675544</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.048771</v>
+        <v>0.16574</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U18" s="24" t="inlineStr">
@@ -6198,7 +6366,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-dkc-nsea-2026-08-05).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6239,32 +6407,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6282,7 +6450,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6292,12 +6460,12 @@
       </c>
       <c r="BC18" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6312,12 +6480,12 @@
       </c>
       <c r="BG18" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:56.857793Z</t>
+          <t>2026-08-05T04:38:10.815485Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6327,13 +6495,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-186</v>
+        <v>-104</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.961538</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.509804</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6375,12 +6543,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>91f1a623718e470b</t>
+          <t>b9619cd820234cc5</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6390,7 +6558,7 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>69512</t>
+          <t>69511</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6400,12 +6568,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6415,7 +6583,7 @@
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J19" s="25" t="n"/>
@@ -6434,21 +6602,21 @@
         <v>0.690402</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.752668</v>
+        <v>0.692195</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.062266</v>
+        <v>0.001793</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U19" s="24" t="inlineStr">
@@ -6467,7 +6635,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6508,32 +6676,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6551,7 +6719,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6561,12 +6729,12 @@
       </c>
       <c r="BC19" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6581,12 +6749,12 @@
       </c>
       <c r="BG19" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:57.357254Z</t>
+          <t>2026-08-05T04:38:12.003217Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6644,22 +6812,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>a5e2f150278e4bf1</t>
+          <t>628efea63f93409f</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00Z</t>
+          <t>2026-08-05T08:00:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>69512</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6669,12 +6837,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6684,7 +6852,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6694,30 +6862,30 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-122</v>
+        <v>-233</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.429185</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.6997</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.6034</v>
+        <v>0.7818929999999999</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.05385</v>
+        <v>0.082193</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U20" s="24" t="inlineStr">
@@ -6736,7 +6904,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6777,32 +6945,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6820,7 +6988,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6830,12 +6998,12 @@
       </c>
       <c r="BC20" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6850,12 +7018,12 @@
       </c>
       <c r="BG20" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:58.482445Z</t>
+          <t>2026-08-05T04:38:12.947438Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6865,13 +7033,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-122</v>
+        <v>-233</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.429185</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.6997</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6913,22 +7081,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>df9b9919858d4118</t>
+          <t>27ca4687f26448c7</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:00:00Z</t>
+          <t>2026-08-05T10:00:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>69539</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6938,12 +7106,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6963,30 +7131,30 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-144</v>
+        <v>-108</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.925926</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.519231</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.831719</v>
+        <v>0.6212029999999999</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.241555</v>
+        <v>0.101972</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U21" s="24" t="inlineStr">
@@ -7005,7 +7173,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7046,32 +7214,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7089,7 +7257,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7099,12 +7267,12 @@
       </c>
       <c r="BC21" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7119,12 +7287,12 @@
       </c>
       <c r="BG21" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:04.870108Z</t>
+          <t>2026-08-05T04:38:15.141988Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7134,13 +7302,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-144</v>
+        <v>-108</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.925926</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.519231</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7182,12 +7350,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>fff580890c974e17</t>
+          <t>7e1b6884e2e441f9</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7232,30 +7400,30 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.480769</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.56154</v>
+        <v>0.549408</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.121011</v>
+        <v>0.06863900000000001</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U22" s="24" t="inlineStr">
@@ -7274,7 +7442,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7358,7 +7526,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7368,12 +7536,12 @@
       </c>
       <c r="BC22" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7388,12 +7556,12 @@
       </c>
       <c r="BG22" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:05.368556Z</t>
+          <t>2026-08-05T04:38:24.231605Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7403,13 +7571,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.480769</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7451,22 +7619,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>901e41bf638b485d</t>
+          <t>50b509ced0b64ae4</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:30:00Z</t>
+          <t>2026-08-05T17:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>69931</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7476,12 +7644,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7501,30 +7669,30 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>2</v>
+        <v>1.884956</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.5</v>
+        <v>0.530516</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.577308</v>
+        <v>0.761888</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.077308</v>
+        <v>0.231372</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U23" s="24" t="inlineStr">
@@ -7543,7 +7711,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7584,32 +7752,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7627,7 +7795,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7637,12 +7805,12 @@
       </c>
       <c r="BC23" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7657,12 +7825,12 @@
       </c>
       <c r="BG23" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:06.503337Z</t>
+          <t>2026-08-05T04:38:25.035543Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7672,13 +7840,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>2</v>
+        <v>1.884956</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.5</v>
+        <v>0.530516</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7720,22 +7888,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>cb80a5f81d224a54</t>
+          <t>9a6437e5e30145e8</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00:00Z</t>
+          <t>2026-08-05T17:30:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>69930</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7745,12 +7913,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7760,7 +7928,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -7770,30 +7938,30 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-127</v>
+        <v>127</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.27</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.440529</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.606257</v>
+        <v>0.560145</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.046786</v>
+        <v>0.119616</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U24" s="24" t="inlineStr">
@@ -7812,7 +7980,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7853,32 +8021,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -7896,7 +8064,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7906,12 +8074,12 @@
       </c>
       <c r="BC24" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7926,12 +8094,12 @@
       </c>
       <c r="BG24" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:11.034551Z</t>
+          <t>2026-08-05T04:38:26.738098Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7941,13 +8109,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-127</v>
+        <v>127</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.27</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.440529</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -7989,22 +8157,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>32b70f3637ee4af5</t>
+          <t>51b544c9d37c4db2</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T20:00:00Z</t>
+          <t>2026-08-05T17:30:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>70301</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8014,12 +8182,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8039,30 +8207,30 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.5</v>
+        <v>0.469484</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.658341</v>
+        <v>0.599621</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.158341</v>
+        <v>0.130137</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U25" s="24" t="inlineStr">
@@ -8081,7 +8249,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8122,32 +8290,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8165,7 +8333,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8175,12 +8343,12 @@
       </c>
       <c r="BC25" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8195,12 +8363,12 @@
       </c>
       <c r="BG25" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:11.579319Z</t>
+          <t>2026-08-05T04:38:27.650106Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8210,13 +8378,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.5</v>
+        <v>0.469484</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8258,22 +8426,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>b0c191ce7ce345d3</t>
+          <t>74650767110d4f6b</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00:00Z</t>
+          <t>2026-08-05T19:00:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8283,12 +8451,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8308,30 +8476,30 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.409836</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.565806</v>
+        <v>0.598431</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.115356</v>
+        <v>0.188595</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U26" s="24" t="inlineStr">
@@ -8350,7 +8518,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8391,32 +8559,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8434,7 +8602,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8444,12 +8612,12 @@
       </c>
       <c r="BC26" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8464,12 +8632,12 @@
       </c>
       <c r="BG26" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:14.606628Z</t>
+          <t>2026-08-05T04:38:33.888149Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8479,13 +8647,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.409836</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8527,22 +8695,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>3baeb1b9f3814ddc</t>
+          <t>8cec84b5ebcf4e06</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.244146Z</t>
+          <t>2026-08-05T04:39:12.089327Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:00:00Z</t>
+          <t>2026-08-05T20:00:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>70301</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8552,12 +8720,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8567,7 +8735,7 @@
       </c>
       <c r="I27" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J27" s="25" t="n"/>
@@ -8577,30 +8745,30 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.75188</v>
+        <v>2</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.589642</v>
+        <v>0.5853390000000001</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.018827</v>
+        <v>0.085339</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U27" s="24" t="inlineStr">
@@ -8619,7 +8787,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8660,32 +8828,32 @@
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8703,7 +8871,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8713,12 +8881,12 @@
       </c>
       <c r="BC27" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8733,12 +8901,12 @@
       </c>
       <c r="BG27" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v5</t>
+          <t>lol-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:16.243697Z</t>
+          <t>2026-08-05T04:38:34.793544Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8748,13 +8916,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.75188</v>
+        <v>2</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8793,6 +8961,2696 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>39d923067e3f455d</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.616766</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.176237</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:38.992546Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>a6f3dbba50e1408a</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>70560</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>ThunderTalk Gaming</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.620532</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.170082</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>ThunderTalk Gaming</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>ThunderTalk Gaming</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>ThunderTalk Gaming</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:44.488114Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>e818bcad4f834ec4</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>70573</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Ground Zero Gaming</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.678987</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.269151</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Ground Zero Gaming</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Ground Zero Gaming</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Ground Zero Gaming</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:46.091265Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>c6af2c10cea0402d</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.55358</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.034349</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-dk-t1-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:47.837724Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>c7d1133479764dd3</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>70788</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.6935249999999999</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.013014</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-ijc-ess-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Esprit Shōnen</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:53.039362Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>3670638ee218445f</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>70790</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.765346</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.175182</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>One More Esports</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:55.077551Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>0a8707f1a18c45e1</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>70860</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.745171</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.145171</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:56.857849Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>a3cee766cadf4f11</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>70862</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.698972</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.029005</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-cg-eko-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Colossal Gaming</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:57.734148Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>8ef77081c6334c10</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.632681</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.032681</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:05.384864Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>e2b2a460c5eb4f44</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:12.089327Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.639259</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.079788</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-vitb-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:09.483653Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS37" headerRowCount="1">
-  <autoFilter ref="A1:CS37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS39" headerRowCount="1">
+  <autoFilter ref="A1:CS39"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$37)</f>
+        <f>COUNTA('Picks'!$A$2:$A$39)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$37)</f>
+        <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS37"/>
+  <dimension ref="A1:CS39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6352,18 +6352,38 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>1.6827</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:21.257965Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-dkc-nsea-2026-08-05).</t>
@@ -6506,8 +6526,12 @@
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
       <c r="BU18" s="25" t="n"/>
@@ -6621,18 +6645,38 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:41:50.735529Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
@@ -6775,8 +6819,12 @@
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
       <c r="BU19" s="25" t="n"/>
@@ -6890,18 +6938,38 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:41:52.466844Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
@@ -6914,7 +6982,7 @@
       </c>
       <c r="AG20" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH20" s="24" t="n"/>
@@ -7044,8 +7112,12 @@
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
       <c r="BU20" s="25" t="n"/>
@@ -7350,12 +7422,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>7e1b6884e2e441f9</t>
+          <t>6e173ced17ed423c</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7400,23 +7472,23 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.490196</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.549408</v>
+        <v>0.54899</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.06863900000000001</v>
+        <v>0.058794</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
@@ -7442,7 +7514,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7526,7 +7598,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7541,7 +7613,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7561,7 +7633,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:24.231605Z</t>
+          <t>2026-08-05T13:56:13.554249Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7571,13 +7643,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.490196</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7619,12 +7691,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>50b509ced0b64ae4</t>
+          <t>9576f1967f7d4d0a</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7678,11 +7750,11 @@
         <v>0.530516</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.761888</v>
+        <v>0.761043</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.231372</v>
+        <v>0.230527</v>
       </c>
       <c r="R23" s="26" t="n">
         <v>100</v>
@@ -7795,7 +7867,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7810,7 +7882,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7830,7 +7902,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:25.035543Z</t>
+          <t>2026-08-05T13:56:15.101150Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7888,12 +7960,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>9a6437e5e30145e8</t>
+          <t>0333ed4ff3274574</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7938,23 +8010,23 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.429185</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.560145</v>
+        <v>0.559679</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.119616</v>
+        <v>0.130494</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S24" s="29" t="n">
         <v>1</v>
@@ -7980,7 +8052,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8064,7 +8136,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8079,7 +8151,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8099,7 +8171,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:26.738098Z</t>
+          <t>2026-08-05T13:56:15.697510Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8109,13 +8181,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.429185</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8157,12 +8229,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>51b544c9d37c4db2</t>
+          <t>8123e23ac6f449cc</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8207,23 +8279,23 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.480769</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.599621</v>
+        <v>0.598983</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.130137</v>
+        <v>0.118214</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="S25" s="29" t="n">
         <v>1.25</v>
@@ -8249,7 +8321,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8333,7 +8405,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8348,7 +8420,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8368,7 +8440,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:27.650106Z</t>
+          <t>2026-08-05T13:56:16.191719Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8378,13 +8450,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.480769</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8426,12 +8498,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>74650767110d4f6b</t>
+          <t>467c4a306f07401e</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8476,23 +8548,23 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.45045</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.598431</v>
+        <v>0.598175</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.188595</v>
+        <v>0.147725</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>1.25</v>
@@ -8518,7 +8590,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8602,7 +8674,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8617,7 +8689,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8637,7 +8709,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:33.888149Z</t>
+          <t>2026-08-05T13:56:20.348944Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8647,13 +8719,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.45045</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8695,12 +8767,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>8cec84b5ebcf4e06</t>
+          <t>2e4c43dae372453a</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8745,23 +8817,23 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>2</v>
+        <v>1.961538</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.5</v>
+        <v>0.509804</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.5853390000000001</v>
+        <v>0.584761</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.085339</v>
+        <v>0.074957</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1.25</v>
@@ -8787,7 +8859,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8871,7 +8943,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8886,7 +8958,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8906,7 +8978,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:34.793544Z</t>
+          <t>2026-08-05T13:56:20.853410Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8916,13 +8988,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>2</v>
+        <v>1.961538</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.5</v>
+        <v>0.509804</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8964,22 +9036,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>39d923067e3f455d</t>
+          <t>3f5510b74f4046e9</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00:00Z</t>
+          <t>2026-08-05T21:00:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -8989,12 +9061,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -9014,26 +9086,26 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>127</v>
+        <v>-170</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.27</v>
+        <v>1.588235</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.62963</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.616766</v>
+        <v>0.670593</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.176237</v>
+        <v>0.040963</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -9056,7 +9128,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9097,32 +9169,32 @@
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -9140,7 +9212,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9155,7 +9227,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9175,7 +9247,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:38.992546Z</t>
+          <t>2026-08-05T13:56:22.599351Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9185,13 +9257,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>127</v>
+        <v>-170</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.27</v>
+        <v>1.588235</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.62963</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9233,22 +9305,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>a6f3dbba50e1408a</t>
+          <t>18a5439372e940bc</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T07:00:00Z</t>
+          <t>2026-08-05T22:00:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9258,12 +9330,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9273,7 +9345,7 @@
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -9283,20 +9355,20 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.440529</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.620532</v>
+        <v>0.616429</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.170082</v>
+        <v>0.1759</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
@@ -9325,7 +9397,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9366,32 +9438,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9409,7 +9481,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9424,7 +9496,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9444,7 +9516,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:44.488114Z</t>
+          <t>2026-08-05T13:56:23.555880Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9454,13 +9526,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.440529</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9502,22 +9574,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>e818bcad4f834ec4</t>
+          <t>99cc9e67af5b40c7</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T09:00:00Z</t>
+          <t>2026-08-06T07:00:00Z</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>70573</t>
+          <t>70560</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9527,12 +9599,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9552,26 +9624,26 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>2.44</v>
+        <v>1.961538</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.509804</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.678987</v>
+        <v>0.6021260000000001</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.269151</v>
+        <v>0.092322</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9594,7 +9666,7 @@
       <c r="AD30" s="24" t="n"/>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9635,32 +9707,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9678,7 +9750,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9693,7 +9765,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9713,7 +9785,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:46.091265Z</t>
+          <t>2026-08-05T13:56:26.928954Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9723,13 +9795,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>2.44</v>
+        <v>1.961538</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.509804</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9771,22 +9843,22 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>c6af2c10cea0402d</t>
+          <t>a8984ef8a4f544ac</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T10:00:00Z</t>
+          <t>2026-08-06T09:00:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>70594</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9796,12 +9868,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9811,7 +9883,7 @@
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J31" s="25" t="n"/>
@@ -9821,26 +9893,26 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-108</v>
+        <v>144</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.44</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.409836</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.55358</v>
+        <v>0.678118</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.034349</v>
+        <v>0.268282</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -9863,7 +9935,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-dk-t1-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9904,32 +9976,32 @@
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -9947,7 +10019,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9962,7 +10034,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9982,7 +10054,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:47.837724Z</t>
+          <t>2026-08-05T13:56:28.210290Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9992,13 +10064,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-108</v>
+        <v>144</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.44</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.409836</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -10040,22 +10112,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>c7d1133479764dd3</t>
+          <t>2ee90d3a91954347</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T16:00:00Z</t>
+          <t>2026-08-06T10:00:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>70788</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10065,12 +10137,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10080,7 +10152,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -10090,26 +10162,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-213</v>
+        <v>-108</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.925926</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.519231</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.6935249999999999</v>
+        <v>0.553149</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.013014</v>
+        <v>0.033918</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10132,7 +10204,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-ijc-ess-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-dk-t1-2026-08-06).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10173,32 +10245,32 @@
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10216,7 +10288,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10231,7 +10303,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10251,7 +10323,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:53.039362Z</t>
+          <t>2026-08-05T13:56:29.341663Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10261,13 +10333,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-213</v>
+        <v>-108</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.925926</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.519231</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10309,12 +10381,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>3670638ee218445f</t>
+          <t>d9c7eea0db7a4b8d</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10324,7 +10396,7 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>70790</t>
+          <t>70788</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -10334,12 +10406,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -10349,7 +10421,7 @@
       </c>
       <c r="I33" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J33" s="25" t="n"/>
@@ -10359,23 +10431,23 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-144</v>
+        <v>-213</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.469484</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.680511</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.765346</v>
+        <v>0.692554</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.175182</v>
+        <v>0.012043</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="S33" s="29" t="n">
         <v>2</v>
@@ -10401,7 +10473,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-ijc-ess-2026-08-06).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10442,32 +10514,32 @@
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -10485,7 +10557,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10500,7 +10572,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10520,7 +10592,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:55.077551Z</t>
+          <t>2026-08-05T13:56:33.192924Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10530,13 +10602,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-144</v>
+        <v>-213</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.469484</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.680511</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10578,22 +10650,22 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>0a8707f1a18c45e1</t>
+          <t>52bccbb01e314316</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T17:00:00Z</t>
+          <t>2026-08-06T16:00:00Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>70860</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10603,12 +10675,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10618,7 +10690,7 @@
       </c>
       <c r="I34" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J34" s="25" t="n"/>
@@ -10628,23 +10700,23 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.745171</v>
+        <v>0.764526</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.145171</v>
+        <v>0.174362</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="S34" s="29" t="n">
         <v>2</v>
@@ -10670,7 +10742,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10711,32 +10783,32 @@
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10754,7 +10826,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10769,7 +10841,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10789,7 +10861,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:56.857849Z</t>
+          <t>2026-08-05T13:56:34.263579Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10799,13 +10871,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -10847,12 +10919,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>a3cee766cadf4f11</t>
+          <t>67685952ecca4474</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -10862,7 +10934,7 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>70862</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -10872,12 +10944,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -10897,23 +10969,23 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.698972</v>
+        <v>0.744077</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.029005</v>
+        <v>0.144077</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="S35" s="29" t="n">
         <v>2</v>
@@ -10939,7 +11011,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-cg-eko-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -10980,32 +11052,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -11023,7 +11095,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11038,7 +11110,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11058,7 +11130,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:57.734148Z</t>
+          <t>2026-08-05T13:56:34.906561Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11068,13 +11140,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-203</v>
+        <v>-150</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.666667</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -11116,22 +11188,22 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>8ef77081c6334c10</t>
+          <t>767eeb6e0f32422b</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-06T17:00:00Z</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>70862</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11141,12 +11213,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11166,26 +11238,26 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>-150</v>
+        <v>-186</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.537634</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.6</v>
+        <v>0.65035</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.632681</v>
+        <v>0.697999</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.032681</v>
+        <v>0.047649</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -11208,7 +11280,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-cg-eko-2026-08-06).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11249,32 +11321,32 @@
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11292,7 +11364,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11307,7 +11379,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11327,7 +11399,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:05.384864Z</t>
+          <t>2026-08-05T13:56:35.496841Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11337,13 +11409,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>-150</v>
+        <v>-186</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.537634</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.6</v>
+        <v>0.65035</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11385,22 +11457,22 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>e2b2a460c5eb4f44</t>
+          <t>f5166443823a4ba9</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T20:00:00Z</t>
+          <t>2026-08-06T18:00:00Z</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>71214</t>
+          <t>70899</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11410,12 +11482,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11425,7 +11497,7 @@
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J37" s="25" t="n"/>
@@ -11435,26 +11507,26 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.639259</v>
+        <v>0.6554720000000001</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.079788</v>
+        <v>0.084657</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -11477,7 +11549,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-vitb-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-tlnp-jl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11518,32 +11590,32 @@
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11561,7 +11633,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11576,7 +11648,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11596,7 +11668,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:09.483653Z</t>
+          <t>2026-08-05T13:56:37.925941Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11606,13 +11678,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11651,6 +11723,544 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>bc04bc9258c34235</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:43.896254Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.631922</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.112691</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Zena Esports</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:39.588429Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>760cad4e94c145b2</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:43.896254Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>71214</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.638828</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>0.079357</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-vitb-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:42.235304Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS39" headerRowCount="1">
-  <autoFilter ref="A1:CS39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS37" headerRowCount="1">
+  <autoFilter ref="A1:CS37"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$39)</f>
+        <f>COUNTA('Picks'!$A$2:$A$37)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$39)</f>
+        <f>SUM('Picks'!$BY$2:$BY$37)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS39"/>
+  <dimension ref="A1:CS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7231,18 +7231,38 @@
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0.000769</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:20.926489Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
@@ -7255,7 +7275,7 @@
       </c>
       <c r="AG21" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH21" s="24" t="n"/>
@@ -7385,8 +7405,12 @@
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.52</v>
+      </c>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
       <c r="BU21" s="25" t="n"/>
@@ -7500,18 +7524,38 @@
       </c>
       <c r="U22" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:26.797637Z</t>
+        </is>
+      </c>
       <c r="AE22" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
@@ -7654,8 +7698,12 @@
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
       <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
       <c r="BU22" s="25" t="n"/>
@@ -7769,18 +7817,38 @@
       </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:28.179885Z</t>
+        </is>
+      </c>
       <c r="AE23" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
@@ -7793,7 +7861,7 @@
       </c>
       <c r="AG23" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH23" s="24" t="n"/>
@@ -7923,8 +7991,12 @@
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
       <c r="BU23" s="25" t="n"/>
@@ -7960,12 +8032,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>0333ed4ff3274574</t>
+          <t>5aba4246ebc54cde</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-05T17:05:09.750488Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7975,7 +8047,7 @@
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>69930</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7985,12 +8057,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -8010,49 +8082,69 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.490196</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.559679</v>
+        <v>0.597761</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.130494</v>
+        <v>0.107565</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="S24" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U24" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:39.894311Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8062,7 +8154,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -8093,32 +8185,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8136,7 +8228,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8151,7 +8243,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8171,7 +8263,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.697510Z</t>
+          <t>2026-08-05T17:04:41.345485Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8181,19 +8273,23 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.490196</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
@@ -8229,22 +8325,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>8123e23ac6f449cc</t>
+          <t>fd5dccee94bf4dc4</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-05T17:05:09.750488Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:30:00Z</t>
+          <t>2026-08-05T19:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>69931</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8254,12 +8350,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8269,7 +8365,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8279,23 +8375,23 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.490196</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.598983</v>
+        <v>0.598437</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.118214</v>
+        <v>0.108241</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="S25" s="29" t="n">
         <v>1.25</v>
@@ -8307,21 +8403,41 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:30.682074Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8362,32 +8478,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8405,7 +8521,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8420,7 +8536,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8440,7 +8556,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:16.191719Z</t>
+          <t>2026-08-05T17:04:46.146013Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8450,19 +8566,23 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.490196</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
@@ -8498,22 +8618,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>467c4a306f07401e</t>
+          <t>f748468d26b045e0</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-05T17:05:09.750488Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00:00Z</t>
+          <t>2026-08-05T21:00:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8523,12 +8643,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8548,26 +8668,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>122</v>
+        <v>-138</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.22</v>
+        <v>1.724638</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.579832</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.598175</v>
+        <v>0.67052</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.147725</v>
+        <v>0.090688</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8576,21 +8696,41 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>1.2681</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:41.224121Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8631,32 +8771,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8674,7 +8814,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8689,7 +8829,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4863ace20696b49ac8d86afb992436652bb1bb2b13aa3380a50818cc662a18c0</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8709,7 +8849,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:20.348944Z</t>
+          <t>2026-08-05T17:04:49.037567Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8719,19 +8859,23 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>122</v>
+        <v>-138</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.22</v>
+        <v>1.724638</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.579832</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
       <c r="BU26" s="25" t="n"/>
@@ -8767,22 +8911,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>2e4c43dae372453a</t>
+          <t>2eb7c6071ec843f9</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-06T00:24:51.570056Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T20:00:00Z</t>
+          <t>2026-08-06T07:00:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>70301</t>
+          <t>70560</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8792,12 +8936,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8817,23 +8961,23 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.584761</v>
+        <v>0.601292</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.074957</v>
+        <v>0.082061</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1.25</v>
@@ -8845,21 +8989,35 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:07.746334Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8869,7 +9027,7 @@
       </c>
       <c r="AG27" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH27" s="24" t="n"/>
@@ -8900,32 +9058,32 @@
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8943,7 +9101,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8958,7 +9116,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8978,7 +9136,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:20.853410Z</t>
+          <t>2026-08-06T00:24:36.724531Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8988,13 +9146,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -9036,22 +9194,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>3f5510b74f4046e9</t>
+          <t>0808601b9aa64343</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-06T00:24:51.570056Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00:00Z</t>
+          <t>2026-08-06T09:00:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -9061,12 +9219,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -9076,7 +9234,7 @@
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -9086,23 +9244,23 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-170</v>
+        <v>117</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.17</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.460829</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.670593</v>
+        <v>0.677029</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.040963</v>
+        <v>0.2162</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="S28" s="29" t="n">
         <v>1.75</v>
@@ -9114,21 +9272,35 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:09.560328Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9138,7 +9310,7 @@
       </c>
       <c r="AG28" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH28" s="24" t="n"/>
@@ -9169,32 +9341,32 @@
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -9212,7 +9384,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9227,7 +9399,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9247,7 +9419,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:22.599351Z</t>
+          <t>2026-08-06T00:24:37.742493Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9257,13 +9429,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-170</v>
+        <v>117</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.17</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.460829</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9305,22 +9477,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>18a5439372e940bc</t>
+          <t>f337824fc1014320</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-06T00:24:51.570056Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00:00Z</t>
+          <t>2026-08-06T16:00:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9330,12 +9502,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9355,26 +9527,26 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.27</v>
+        <v>1.694444</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.590164</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.616429</v>
+        <v>0.764249</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.1759</v>
+        <v>0.174085</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9383,21 +9555,35 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:11.315585Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9438,32 +9624,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9481,7 +9667,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9496,7 +9682,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9516,7 +9702,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:23.555880Z</t>
+          <t>2026-08-06T00:24:42.381233Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9526,13 +9712,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.27</v>
+        <v>1.694444</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.590164</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9574,22 +9760,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>99cc9e67af5b40c7</t>
+          <t>19c128d8df7b49bb</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-06T00:24:51.570056Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T07:00:00Z</t>
+          <t>2026-08-06T17:00:00Z</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9599,12 +9785,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9624,26 +9810,26 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-104</v>
+        <v>-150</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.666667</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.6</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.6021260000000001</v>
+        <v>0.742815</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.092322</v>
+        <v>0.142815</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9652,21 +9838,35 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:13.006126Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9676,7 +9876,7 @@
       </c>
       <c r="AG30" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH30" s="24" t="n"/>
@@ -9707,32 +9907,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9750,7 +9950,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9765,7 +9965,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9785,7 +9985,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:26.928954Z</t>
+          <t>2026-08-06T00:24:43.466107Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9795,13 +9995,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>-104</v>
+        <v>-150</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.666667</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.6</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9843,22 +10043,22 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>a8984ef8a4f544ac</t>
+          <t>fab2311131514378</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-06T00:24:51.570056Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T09:00:00Z</t>
+          <t>2026-08-06T18:00:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>70573</t>
+          <t>70903</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9868,12 +10068,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9893,26 +10093,26 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.469484</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.678118</v>
+        <v>0.630956</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.268282</v>
+        <v>0.161472</v>
       </c>
       <c r="R31" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -9921,21 +10121,35 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:14.772492Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9976,32 +10190,32 @@
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -10019,7 +10233,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -10034,7 +10248,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>4304963c152f1e881f634fa0b66ab59152f3edd6692257c1d27d76a5cb0a3df3</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -10054,7 +10268,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:28.210290Z</t>
+          <t>2026-08-06T00:24:47.491847Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -10064,13 +10278,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.469484</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -10112,22 +10326,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>2ee90d3a91954347</t>
+          <t>a2df408e417748e0</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-07T15:24:10.407714Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T10:00:00Z</t>
+          <t>2026-08-07T16:00:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>70594</t>
+          <t>71980</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10137,12 +10351,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Aeterna Esports</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10152,7 +10366,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -10162,26 +10376,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-108</v>
+        <v>-117</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.854701</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.539171</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.553149</v>
+        <v>0.637212</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.033918</v>
+        <v>0.098041</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10204,7 +10418,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-dk-t1-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-aee-tts-2026-08-07).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10245,32 +10459,32 @@
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>TITANS</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Aeterna Esports</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Aeterna Esports</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Aeterna Esports</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10288,7 +10502,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10303,7 +10517,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10323,7 +10537,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:29.341663Z</t>
+          <t>2026-08-07T15:23:54.049058Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10333,13 +10547,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-108</v>
+        <v>-117</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.854701</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.539171</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10381,22 +10595,22 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>d9c7eea0db7a4b8d</t>
+          <t>949e6b907de14c9c</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-07T15:24:10.407714Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T16:00:00Z</t>
+          <t>2026-08-07T19:00:00Z</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>70788</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -10406,12 +10620,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -10431,26 +10645,26 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-213</v>
+        <v>117</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.17</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.460829</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.692554</v>
+        <v>0.576745</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.012043</v>
+        <v>0.115916</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -10473,7 +10687,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-ijc-ess-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-gmb-cg-2026-08-07).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10514,32 +10728,32 @@
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -10557,7 +10771,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10572,7 +10786,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10592,7 +10806,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:33.192924Z</t>
+          <t>2026-08-07T15:23:56.287371Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10602,13 +10816,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-213</v>
+        <v>117</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.17</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.460829</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10650,22 +10864,22 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>52bccbb01e314316</t>
+          <t>f36d76ff9dcf4fa5</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-07T15:24:10.407714Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T16:00:00Z</t>
+          <t>2026-08-07T21:00:00Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>70790</t>
+          <t>72428</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10675,12 +10889,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Vivo Keyd Stars</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10690,7 +10904,7 @@
       </c>
       <c r="I34" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J34" s="25" t="n"/>
@@ -10700,20 +10914,20 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-144</v>
+        <v>108</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.08</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.480769</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.764526</v>
+        <v>0.6956059999999999</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.174362</v>
+        <v>0.214837</v>
       </c>
       <c r="R34" s="26" t="n">
         <v>100</v>
@@ -10742,7 +10956,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-vks-fxw7-2026-08-07).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10783,32 +10997,32 @@
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Vivo Keyd Stars</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Vivo Keyd Stars</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Vivo Keyd Stars</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10826,7 +11040,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10841,7 +11055,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10861,7 +11075,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:34.263579Z</t>
+          <t>2026-08-07T15:23:56.826662Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10871,13 +11085,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>-144</v>
+        <v>108</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.08</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.480769</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -10919,22 +11133,22 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>67685952ecca4474</t>
+          <t>c2dc7e7805034936</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-07T15:24:10.407714Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T17:00:00Z</t>
+          <t>2026-08-07T21:00:00Z</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>70860</t>
+          <t>72438</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -10944,12 +11158,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Dorado Gaming</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -10959,7 +11173,7 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J35" s="25" t="n"/>
@@ -10969,26 +11183,26 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-150</v>
+        <v>108</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.08</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.6</v>
+        <v>0.480769</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.744077</v>
+        <v>0.627435</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.144077</v>
+        <v>0.146666</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
@@ -11011,7 +11225,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-blue-dog-2026-08-07).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -11052,32 +11266,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Dorado Gaming</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Dorado Gaming</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Dorado Gaming</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -11095,7 +11309,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11110,7 +11324,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11130,7 +11344,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:34.906561Z</t>
+          <t>2026-08-07T15:23:57.410433Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11140,13 +11354,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-150</v>
+        <v>108</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.08</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.6</v>
+        <v>0.480769</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -11188,22 +11402,22 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>767eeb6e0f32422b</t>
+          <t>8ce9d562fa1e4050</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-07T15:24:10.407714Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T17:00:00Z</t>
+          <t>2026-08-08T08:00:00Z</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>70862</t>
+          <t>72722</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11213,12 +11427,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11238,26 +11452,26 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>-186</v>
+        <v>113</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.13</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.469484</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.697999</v>
+        <v>0.605705</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.047649</v>
+        <v>0.136221</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -11280,7 +11494,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-cg-eko-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-t1-hle-2026-08-08).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11321,32 +11535,32 @@
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11364,7 +11578,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11379,7 +11593,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11399,7 +11613,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:35.496841Z</t>
+          <t>2026-08-07T15:23:59.567486Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11409,13 +11623,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>-186</v>
+        <v>113</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.13</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.469484</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11457,22 +11671,22 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>f5166443823a4ba9</t>
+          <t>1453b4854d604831</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
+          <t>2026-08-07T15:24:10.407714Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-08T16:00:00Z</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>70899</t>
+          <t>72871</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11482,12 +11696,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>paiN Gaming</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>RED Canids</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11507,26 +11721,26 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-133</v>
+        <v>104</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.04</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.490196</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.6554720000000001</v>
+        <v>0.692705</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.084657</v>
+        <v>0.202509</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -11549,7 +11763,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-tlnp-jl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-red-png-2026-08-08).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11590,32 +11804,32 @@
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>paiN Gaming</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>paiN Gaming</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>paiN Gaming</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>RED Canids</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>RED Canids</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>RED Canids</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11633,7 +11847,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11648,7 +11862,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
+          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11668,7 +11882,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:37.925941Z</t>
+          <t>2026-08-07T15:24:07.921330Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11678,13 +11892,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-133</v>
+        <v>104</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.04</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.490196</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11723,544 +11937,6 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>bc04bc9258c34235</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>70903</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>Zena Esports</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L38" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N38" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O38" s="28" t="n">
-        <v>0.631922</v>
-      </c>
-      <c r="P38" s="28" t="n"/>
-      <c r="Q38" s="28" t="n">
-        <v>0.112691</v>
-      </c>
-      <c r="R38" s="26" t="n">
-        <v>76</v>
-      </c>
-      <c r="S38" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T38" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U38" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
-      <c r="AE38" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
-        </is>
-      </c>
-      <c r="AF38" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG38" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH38" s="24" t="n"/>
-      <c r="AI38" s="31" t="n"/>
-      <c r="AJ38" s="31" t="n"/>
-      <c r="AK38" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL38" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM38" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN38" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO38" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP38" s="24" t="inlineStr">
-        <is>
-          <t>Zena Esports</t>
-        </is>
-      </c>
-      <c r="AQ38" s="24" t="inlineStr">
-        <is>
-          <t>Zena Esports</t>
-        </is>
-      </c>
-      <c r="AR38" s="24" t="inlineStr">
-        <is>
-          <t>Zena Esports</t>
-        </is>
-      </c>
-      <c r="AS38" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="AT38" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="AU38" s="24" t="inlineStr">
-        <is>
-          <t>GMBLERS ESPORTS</t>
-        </is>
-      </c>
-      <c r="AV38" s="24" t="n"/>
-      <c r="AW38" s="24" t="n"/>
-      <c r="AX38" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY38" s="24" t="n"/>
-      <c r="AZ38" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA38" s="24" t="inlineStr">
-        <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
-        </is>
-      </c>
-      <c r="BB38" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC38" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD38" s="24" t="inlineStr">
-        <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
-        </is>
-      </c>
-      <c r="BE38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG38" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH38" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:56:39.588429Z</t>
-        </is>
-      </c>
-      <c r="BI38" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ38" s="25" t="n"/>
-      <c r="BK38" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL38" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM38" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN38" s="28" t="n"/>
-      <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
-      <c r="BR38" s="28" t="n"/>
-      <c r="BS38" s="28" t="n"/>
-      <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
-      <c r="BV38" s="29" t="n"/>
-      <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
-      <c r="BZ38" s="24" t="n"/>
-      <c r="CA38" s="31" t="n"/>
-      <c r="CB38" s="24" t="n"/>
-      <c r="CC38" s="24" t="n"/>
-      <c r="CD38" s="24" t="n"/>
-      <c r="CE38" s="24" t="n"/>
-      <c r="CF38" s="24" t="n"/>
-      <c r="CG38" s="24" t="n"/>
-      <c r="CH38" s="24" t="n"/>
-      <c r="CI38" s="24" t="n"/>
-      <c r="CJ38" s="24" t="n"/>
-      <c r="CK38" s="24" t="n"/>
-      <c r="CL38" s="24" t="n"/>
-      <c r="CM38" s="24" t="n"/>
-      <c r="CN38" s="24" t="n"/>
-      <c r="CO38" s="24" t="n"/>
-      <c r="CP38" s="24" t="n"/>
-      <c r="CQ38" s="24" t="n"/>
-      <c r="CR38" s="24" t="n"/>
-      <c r="CS38" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>760cad4e94c145b2</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:56:43.896254Z</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>71214</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="N39" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="O39" s="28" t="n">
-        <v>0.638828</v>
-      </c>
-      <c r="P39" s="28" t="n"/>
-      <c r="Q39" s="28" t="n">
-        <v>0.079357</v>
-      </c>
-      <c r="R39" s="26" t="n">
-        <v>60</v>
-      </c>
-      <c r="S39" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T39" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U39" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="28" t="n"/>
-      <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
-      <c r="AE39" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-vitb-2026-08-06).</t>
-        </is>
-      </c>
-      <c r="AF39" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG39" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH39" s="24" t="n"/>
-      <c r="AI39" s="31" t="n"/>
-      <c r="AJ39" s="31" t="n"/>
-      <c r="AK39" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL39" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM39" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN39" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO39" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP39" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AQ39" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AR39" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AS39" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AT39" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AU39" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AV39" s="24" t="n"/>
-      <c r="AW39" s="24" t="n"/>
-      <c r="AX39" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY39" s="24" t="n"/>
-      <c r="AZ39" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA39" s="24" t="inlineStr">
-        <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
-        </is>
-      </c>
-      <c r="BB39" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC39" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD39" s="24" t="inlineStr">
-        <is>
-          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
-        </is>
-      </c>
-      <c r="BE39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG39" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH39" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:56:42.235304Z</t>
-        </is>
-      </c>
-      <c r="BI39" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ39" s="25" t="n"/>
-      <c r="BK39" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="BL39" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="BM39" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN39" s="28" t="n"/>
-      <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
-      <c r="BR39" s="28" t="n"/>
-      <c r="BS39" s="28" t="n"/>
-      <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
-      <c r="BV39" s="29" t="n"/>
-      <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
-      <c r="BZ39" s="24" t="n"/>
-      <c r="CA39" s="31" t="n"/>
-      <c r="CB39" s="24" t="n"/>
-      <c r="CC39" s="24" t="n"/>
-      <c r="CD39" s="24" t="n"/>
-      <c r="CE39" s="24" t="n"/>
-      <c r="CF39" s="24" t="n"/>
-      <c r="CG39" s="24" t="n"/>
-      <c r="CH39" s="24" t="n"/>
-      <c r="CI39" s="24" t="n"/>
-      <c r="CJ39" s="24" t="n"/>
-      <c r="CK39" s="24" t="n"/>
-      <c r="CL39" s="24" t="n"/>
-      <c r="CM39" s="24" t="n"/>
-      <c r="CN39" s="24" t="n"/>
-      <c r="CO39" s="24" t="n"/>
-      <c r="CP39" s="24" t="n"/>
-      <c r="CQ39" s="24" t="n"/>
-      <c r="CR39" s="24" t="n"/>
-      <c r="CS39" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/lol.xlsx
+++ b/data/gated_research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS37" headerRowCount="1">
-  <autoFilter ref="A1:CS37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
+  <autoFilter ref="A1:CS38"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$37)</f>
+        <f>COUNTA('Picks'!$A$2:$A$38)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$37,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$37,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")/(COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"win")+COUNTIFS('Picks'!$BX$2:$BX$37,"&gt;0",'Picks'!$V$2:$V$37,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$37)/SUM('Picks'!$BX$2:$BX$37),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$37)</f>
+        <f>SUM('Picks'!$BY$2:$BY$38)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$37,"&lt;&gt;",'Picks'!$AB$2:$AB$37),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$37,'Picks'!$AM$2:$AM$37,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A14,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A15,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled",'Picks'!$V$2:$V$37,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$37,'Picks'!$H$2:$H$37,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$37,'Picks'!$H$2:$H$37,$A16,'Picks'!$U$2:$U$37,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS37"/>
+  <dimension ref="A1:CS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10404,18 +10404,38 @@
       </c>
       <c r="U32" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y32" s="25" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="28" t="n"/>
-      <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
-      <c r="AD32" s="24" t="n"/>
+      <c r="Z32" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:28.802280Z</t>
+        </is>
+      </c>
       <c r="AE32" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-aee-tts-2026-08-07).</t>
@@ -10558,8 +10578,12 @@
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
       <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
-      <c r="BR32" s="28" t="n"/>
+      <c r="BQ32" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR32" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
       <c r="BU32" s="25" t="n"/>
@@ -10595,12 +10619,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>949e6b907de14c9c</t>
+          <t>08d6e9eb272449c2</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10654,11 +10678,11 @@
         <v>0.460829</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.576745</v>
+        <v>0.576862</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.115916</v>
+        <v>0.116033</v>
       </c>
       <c r="R33" s="26" t="n">
         <v>78</v>
@@ -10771,7 +10795,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10786,7 +10810,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10806,7 +10830,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:56.287371Z</t>
+          <t>2026-08-07T18:31:07.695348Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10864,12 +10888,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>f36d76ff9dcf4fa5</t>
+          <t>61b949111ab54871</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10923,11 +10947,11 @@
         <v>0.480769</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.6956059999999999</v>
+        <v>0.695648</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.214837</v>
+        <v>0.214879</v>
       </c>
       <c r="R34" s="26" t="n">
         <v>100</v>
@@ -11040,7 +11064,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -11055,7 +11079,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -11075,7 +11099,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:56.826662Z</t>
+          <t>2026-08-07T18:31:08.212012Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -11133,12 +11157,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>c2dc7e7805034936</t>
+          <t>b2976f2bae944bad</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -11192,11 +11216,11 @@
         <v>0.480769</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.627435</v>
+        <v>0.627171</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.146666</v>
+        <v>0.146402</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>93</v>
@@ -11309,7 +11333,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11324,7 +11348,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11344,7 +11368,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:57.410433Z</t>
+          <t>2026-08-07T18:31:08.974236Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11402,12 +11426,12 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>8ce9d562fa1e4050</t>
+          <t>56161deaedb746eb</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -11452,23 +11476,23 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.490196</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.605705</v>
+        <v>0.605845</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.136221</v>
+        <v>0.115649</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="S36" s="29" t="n">
         <v>1.25</v>
@@ -11494,7 +11518,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-t1-hle-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-t1-hle-2026-08-08).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11578,7 +11602,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11593,7 +11617,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11613,7 +11637,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:59.567486Z</t>
+          <t>2026-08-07T18:31:11.080798Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11623,13 +11647,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.490196</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11671,22 +11695,22 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>1453b4854d604831</t>
+          <t>906dd91507e34909</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-08T16:00:00Z</t>
+          <t>2026-08-08T11:00:00Z</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>72871</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11696,12 +11720,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11721,26 +11745,26 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>104</v>
+        <v>-138</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>2.04</v>
+        <v>1.724638</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.579832</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.692705</v>
+        <v>0.675074</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.202509</v>
+        <v>0.09524199999999999</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -11763,7 +11787,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-red-png-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-gls-els-2026-08-08).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11804,32 +11828,32 @@
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11847,7 +11871,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11862,7 +11886,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11882,7 +11906,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:07.921330Z</t>
+          <t>2026-08-07T18:31:14.111862Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11892,13 +11916,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>104</v>
+        <v>-138</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>2.04</v>
+        <v>1.724638</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.579832</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11937,6 +11961,275 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>c051521d6c394e62</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:20.691239Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>72871</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.6928530000000001</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.202657</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-red-png-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:18.039096Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
